--- a/awim/cal slayer 0.5 zoom.xlsx
+++ b/awim/cal slayer 0.5 zoom.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/640dce341da437cb/02 Time v3 physical Clock/Time v3 Clock camera and image processing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E488AC-2BBB-4467-A89D-5DC6DB7C0010}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F30152-0561-4676-BE96-85966EAA726C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="cal new slayer mobile 16 to 9" sheetId="1" r:id="rId1"/>
+    <sheet name="calibration" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -21,18 +21,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="51">
-  <si>
-    <t>az_sect</t>
-  </si>
-  <si>
-    <t>alt_sect</t>
-  </si>
-  <si>
-    <t>az_rel</t>
-  </si>
-  <si>
-    <t>alt_rel</t>
-  </si>
   <si>
     <t>rec_x</t>
   </si>
@@ -52,22 +40,10 @@
     <t>out2</t>
   </si>
   <si>
-    <t>az_total</t>
-  </si>
-  <si>
-    <t>alt_total</t>
-  </si>
-  <si>
     <t>px_x</t>
   </si>
   <si>
     <t>px_y</t>
-  </si>
-  <si>
-    <t>az</t>
-  </si>
-  <si>
-    <t>alt</t>
   </si>
   <si>
     <t>camera_name</t>
@@ -130,9 +106,6 @@
     <t>target_right</t>
   </si>
   <si>
-    <t>target_pos_azalt_relaim</t>
-  </si>
-  <si>
     <t>target_center_calculated_from_edges</t>
   </si>
   <si>
@@ -173,6 +146,33 @@
   </si>
   <si>
     <t>LB</t>
+  </si>
+  <si>
+    <t>target_pos_xysph_relaim</t>
+  </si>
+  <si>
+    <t>xsph_sect</t>
+  </si>
+  <si>
+    <t>ysph_sect</t>
+  </si>
+  <si>
+    <t>xsph_rel</t>
+  </si>
+  <si>
+    <t>ysph_rel</t>
+  </si>
+  <si>
+    <t>xsph_total</t>
+  </si>
+  <si>
+    <t>ysph_total</t>
+  </si>
+  <si>
+    <t>xsph</t>
+  </si>
+  <si>
+    <t>ysph</t>
   </si>
 </sst>
 </file>
@@ -1049,10 +1049,8 @@
   <dimension ref="A1:P592"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32.6640625" bestFit="1" customWidth="1"/>
@@ -1066,52 +1064,52 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -1122,10 +1120,10 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1148,7 +1146,7 @@
         <v>3000</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1168,10 +1166,10 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1190,7 +1188,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1210,7 +1208,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
@@ -1234,7 +1232,7 @@
         <v>2250</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1254,10 +1252,10 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1276,10 +1274,10 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1298,10 +1296,10 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1320,7 +1318,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -1354,10 +1352,10 @@
         <v>-1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1384,10 +1382,10 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1418,10 +1416,10 @@
         <v>2004</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1452,10 +1450,10 @@
         <v>1989</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1486,10 +1484,10 @@
         <v>2020</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1520,10 +1518,10 @@
         <v>2004</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1554,10 +1552,10 @@
         <v>2004</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1584,10 +1582,10 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1614,10 +1612,10 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1648,10 +1646,10 @@
         <v>2654</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1682,10 +1680,10 @@
         <v>2653</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1716,10 +1714,10 @@
         <v>2653</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1746,10 +1744,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1776,10 +1774,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1810,10 +1808,10 @@
         <v>1991</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1844,10 +1842,10 @@
         <v>2022</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1878,10 +1876,10 @@
         <v>2006</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1908,10 +1906,10 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1938,10 +1936,10 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -1972,7 +1970,7 @@
         <v>2160</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -2004,7 +2002,7 @@
         <v>2320</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -2036,7 +2034,7 @@
         <v>2482</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -2068,7 +2066,7 @@
         <v>2004</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2100,7 +2098,7 @@
         <v>2160</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2132,7 +2130,7 @@
         <v>2320</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2164,7 +2162,7 @@
         <v>2482</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2196,7 +2194,7 @@
         <v>2006</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2228,7 +2226,7 @@
         <v>2162</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2260,7 +2258,7 @@
         <v>2321</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2292,7 +2290,7 @@
         <v>2483</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -2320,10 +2318,10 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -2354,10 +2352,10 @@
         <v>2660</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -2388,10 +2386,10 @@
         <v>2643</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -2422,10 +2420,10 @@
         <v>2678</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -2456,10 +2454,10 @@
         <v>2659</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -2490,10 +2488,10 @@
         <v>2660</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2520,10 +2518,10 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -2550,10 +2548,10 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -2584,10 +2582,10 @@
         <v>3496</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -2618,10 +2616,10 @@
         <v>3494</v>
       </c>
       <c r="G51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2652,10 +2650,10 @@
         <v>3493</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -2682,10 +2680,10 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -2712,10 +2710,10 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -2746,10 +2744,10 @@
         <v>2630</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -2780,10 +2778,10 @@
         <v>2665</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -2814,10 +2812,10 @@
         <v>2647</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -2844,10 +2842,10 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -2874,10 +2872,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -2908,7 +2906,7 @@
         <v>2840</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -2940,7 +2938,7 @@
         <v>3036</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2972,7 +2970,7 @@
         <v>3250</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -3004,7 +3002,7 @@
         <v>2655</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -3036,7 +3034,7 @@
         <v>2834</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -3068,7 +3066,7 @@
         <v>3030</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -3100,7 +3098,7 @@
         <v>3243</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -3132,7 +3130,7 @@
         <v>2652</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -3164,7 +3162,7 @@
         <v>2831</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -3196,7 +3194,7 @@
         <v>3025</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -3228,7 +3226,7 @@
         <v>3238</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -3256,10 +3254,10 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -3290,10 +3288,10 @@
         <v>3570</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -3324,10 +3322,10 @@
         <v>3542</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -3358,10 +3356,10 @@
         <v>3597</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -3392,10 +3390,10 @@
         <v>3568</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -3426,10 +3424,10 @@
         <v>3571</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -3456,10 +3454,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -3486,10 +3484,10 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -3516,10 +3514,10 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -3546,10 +3544,10 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -3576,10 +3574,10 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -3606,10 +3604,10 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -3636,10 +3634,10 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -3670,10 +3668,10 @@
         <v>3497</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -3704,10 +3702,10 @@
         <v>3552</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -3738,10 +3736,10 @@
         <v>3523</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -3768,10 +3766,10 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -3798,10 +3796,10 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -3832,7 +3830,7 @@
         <v>3862</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -3860,7 +3858,7 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -3888,7 +3886,7 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -3920,7 +3918,7 @@
         <v>3553</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -3952,7 +3950,7 @@
         <v>3842</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -3980,7 +3978,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -4008,7 +4006,7 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -4040,7 +4038,7 @@
         <v>3539</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -4072,7 +4070,7 @@
         <v>3827</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -4100,7 +4098,7 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -4128,7 +4126,7 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -4156,10 +4154,10 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -4186,10 +4184,10 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -4216,10 +4214,10 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -4246,10 +4244,10 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -4276,10 +4274,10 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -4306,10 +4304,10 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -4336,10 +4334,10 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -4366,10 +4364,10 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -4396,10 +4394,10 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -4426,10 +4424,10 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H109" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -4456,10 +4454,10 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -4486,10 +4484,10 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -4516,10 +4514,10 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -4546,10 +4544,10 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -4576,10 +4574,10 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -4606,10 +4604,10 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -4636,10 +4634,10 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -4666,10 +4664,10 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -4696,7 +4694,7 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -4724,7 +4722,7 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -4752,7 +4750,7 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
@@ -4780,7 +4778,7 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -4808,7 +4806,7 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
@@ -4836,7 +4834,7 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
@@ -4864,7 +4862,7 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -4892,7 +4890,7 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
@@ -4920,7 +4918,7 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
@@ -4948,7 +4946,7 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -4976,7 +4974,7 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
@@ -5004,10 +5002,10 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
@@ -5034,10 +5032,10 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -5064,10 +5062,10 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -5094,10 +5092,10 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -5124,10 +5122,10 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -5154,10 +5152,10 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -5184,10 +5182,10 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -5214,10 +5212,10 @@
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H136" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -5244,10 +5242,10 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -5274,10 +5272,10 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H138" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -5304,10 +5302,10 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -5334,10 +5332,10 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -5364,10 +5362,10 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
@@ -5394,10 +5392,10 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -5424,10 +5422,10 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -5454,10 +5452,10 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -5484,10 +5482,10 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -5514,10 +5512,10 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -5544,7 +5542,7 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
@@ -5572,7 +5570,7 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
@@ -5600,7 +5598,7 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
@@ -5628,7 +5626,7 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
@@ -5656,7 +5654,7 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
@@ -5684,7 +5682,7 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
@@ -5712,7 +5710,7 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -5740,7 +5738,7 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -5768,7 +5766,7 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -5796,7 +5794,7 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -5824,7 +5822,7 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
@@ -5852,10 +5850,10 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -5886,10 +5884,10 @@
         <v>2012</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -5920,10 +5918,10 @@
         <v>1996</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -5954,10 +5952,10 @@
         <v>2028</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
@@ -5988,10 +5986,10 @@
         <v>2011</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
@@ -6022,10 +6020,10 @@
         <v>2011</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -6052,10 +6050,10 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -6082,10 +6080,10 @@
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H165" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -6116,10 +6114,10 @@
         <v>2685</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -6150,10 +6148,10 @@
         <v>2682</v>
       </c>
       <c r="G167" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H167" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H167" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
@@ -6184,10 +6182,10 @@
         <v>2683</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
@@ -6214,10 +6212,10 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
@@ -6244,10 +6242,10 @@
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
@@ -6278,10 +6276,10 @@
         <v>1989</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -6312,10 +6310,10 @@
         <v>2025</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -6346,10 +6344,10 @@
         <v>2006</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -6376,10 +6374,10 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
@@ -6406,10 +6404,10 @@
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
@@ -6440,7 +6438,7 @@
         <v>2173</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -6472,7 +6470,7 @@
         <v>2338</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -6504,7 +6502,7 @@
         <v>2507</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
@@ -6536,7 +6534,7 @@
         <v>2010</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
@@ -6568,7 +6566,7 @@
         <v>2176</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -6600,7 +6598,7 @@
         <v>2344</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
@@ -6632,7 +6630,7 @@
         <v>2515</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
@@ -6664,7 +6662,7 @@
         <v>2008</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
@@ -6696,7 +6694,7 @@
         <v>2178</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
@@ -6728,7 +6726,7 @@
         <v>2351</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
@@ -6760,7 +6758,7 @@
         <v>2527</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
@@ -6788,10 +6786,10 @@
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
@@ -6822,10 +6820,10 @@
         <v>2684</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
@@ -6856,10 +6854,10 @@
         <v>2666</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
@@ -6890,10 +6888,10 @@
         <v>2702</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
@@ -6924,10 +6922,10 @@
         <v>2684</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I191" s="1"/>
       <c r="J191" s="1"/>
@@ -6958,10 +6956,10 @@
         <v>2683</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
@@ -6988,10 +6986,10 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I193" s="1"/>
       <c r="J193" s="1"/>
@@ -7018,10 +7016,10 @@
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H194" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I194" s="1"/>
       <c r="J194" s="1"/>
@@ -7052,10 +7050,10 @@
         <v>3544</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I195" s="1"/>
       <c r="J195" s="1"/>
@@ -7086,10 +7084,10 @@
         <v>3539</v>
       </c>
       <c r="G196" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H196" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I196" s="1"/>
       <c r="J196" s="1"/>
@@ -7120,10 +7118,10 @@
         <v>3541</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I197" s="1"/>
       <c r="J197" s="1"/>
@@ -7150,10 +7148,10 @@
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I198" s="1"/>
       <c r="J198" s="1"/>
@@ -7180,10 +7178,10 @@
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I199" s="1"/>
       <c r="J199" s="1"/>
@@ -7214,10 +7212,10 @@
         <v>2693</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I200" s="1"/>
       <c r="J200" s="1"/>
@@ -7248,10 +7246,10 @@
         <v>2732</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I201" s="1"/>
       <c r="J201" s="1"/>
@@ -7282,10 +7280,10 @@
         <v>2712</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I202" s="1"/>
       <c r="J202" s="1"/>
@@ -7312,10 +7310,10 @@
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I203" s="1"/>
       <c r="J203" s="1"/>
@@ -7342,10 +7340,10 @@
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
@@ -7376,7 +7374,7 @@
         <v>2870</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H205" s="1"/>
       <c r="I205" s="1"/>
@@ -7408,7 +7406,7 @@
         <v>3073</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
@@ -7440,7 +7438,7 @@
         <v>3292</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
@@ -7472,7 +7470,7 @@
         <v>2693</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
@@ -7504,7 +7502,7 @@
         <v>2882</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
@@ -7536,7 +7534,7 @@
         <v>3090</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
@@ -7568,7 +7566,7 @@
         <v>3316</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
@@ -7600,7 +7598,7 @@
         <v>2703</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
@@ -7632,7 +7630,7 @@
         <v>2898</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
@@ -7664,7 +7662,7 @@
         <v>3109</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
@@ -7696,7 +7694,7 @@
         <v>3342</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
@@ -7724,10 +7722,10 @@
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I216" s="1"/>
       <c r="J216" s="1"/>
@@ -7758,10 +7756,10 @@
         <v>3519</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
@@ -7792,10 +7790,10 @@
         <v>3494</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I218" s="1"/>
       <c r="J218" s="1"/>
@@ -7826,10 +7824,10 @@
         <v>3546</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I219" s="1"/>
       <c r="J219" s="1"/>
@@ -7860,10 +7858,10 @@
         <v>3521</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I220" s="1"/>
       <c r="J220" s="1"/>
@@ -7894,10 +7892,10 @@
         <v>3517</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I221" s="1"/>
       <c r="J221" s="1"/>
@@ -7924,10 +7922,10 @@
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I222" s="1"/>
       <c r="J222" s="1"/>
@@ -7954,10 +7952,10 @@
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H223" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H223" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I223" s="1"/>
       <c r="J223" s="1"/>
@@ -7984,10 +7982,10 @@
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I224" s="1"/>
       <c r="J224" s="1"/>
@@ -8014,10 +8012,10 @@
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H225" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H225" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
@@ -8044,10 +8042,10 @@
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I226" s="1"/>
       <c r="J226" s="1"/>
@@ -8074,10 +8072,10 @@
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I227" s="1"/>
       <c r="J227" s="1"/>
@@ -8104,10 +8102,10 @@
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I228" s="1"/>
       <c r="J228" s="1"/>
@@ -8134,10 +8132,10 @@
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I229" s="1"/>
       <c r="J229" s="1"/>
@@ -8164,10 +8162,10 @@
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I230" s="1"/>
       <c r="J230" s="1"/>
@@ -8194,10 +8192,10 @@
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I231" s="1"/>
       <c r="J231" s="1"/>
@@ -8224,10 +8222,10 @@
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I232" s="1"/>
       <c r="J232" s="1"/>
@@ -8254,10 +8252,10 @@
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I233" s="1"/>
       <c r="J233" s="1"/>
@@ -8288,7 +8286,7 @@
         <v>3797</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
@@ -8316,7 +8314,7 @@
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
@@ -8344,7 +8342,7 @@
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
@@ -8376,7 +8374,7 @@
         <v>3529</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
@@ -8408,7 +8406,7 @@
         <v>3813</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
@@ -8436,7 +8434,7 @@
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
@@ -8464,7 +8462,7 @@
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
@@ -8496,7 +8494,7 @@
         <v>3543</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
@@ -8528,7 +8526,7 @@
         <v>3837</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
@@ -8556,7 +8554,7 @@
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
@@ -8584,7 +8582,7 @@
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
@@ -8612,10 +8610,10 @@
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I245" s="1"/>
       <c r="J245" s="1"/>
@@ -8642,10 +8640,10 @@
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I246" s="1"/>
       <c r="J246" s="1"/>
@@ -8672,10 +8670,10 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I247" s="1"/>
       <c r="J247" s="1"/>
@@ -8702,10 +8700,10 @@
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I248" s="1"/>
       <c r="J248" s="1"/>
@@ -8732,10 +8730,10 @@
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I249" s="1"/>
       <c r="J249" s="1"/>
@@ -8762,10 +8760,10 @@
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
@@ -8792,10 +8790,10 @@
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I251" s="1"/>
       <c r="J251" s="1"/>
@@ -8822,10 +8820,10 @@
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H252" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H252" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I252" s="1"/>
       <c r="J252" s="1"/>
@@ -8852,10 +8850,10 @@
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
@@ -8882,10 +8880,10 @@
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H254" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H254" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
@@ -8912,10 +8910,10 @@
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
@@ -8942,10 +8940,10 @@
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
@@ -8972,10 +8970,10 @@
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
@@ -9002,10 +9000,10 @@
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -9032,10 +9030,10 @@
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
@@ -9062,10 +9060,10 @@
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
@@ -9092,10 +9090,10 @@
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
@@ -9122,10 +9120,10 @@
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
@@ -9152,7 +9150,7 @@
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
@@ -9180,7 +9178,7 @@
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
@@ -9208,7 +9206,7 @@
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
@@ -9236,7 +9234,7 @@
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
@@ -9264,7 +9262,7 @@
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
@@ -9292,7 +9290,7 @@
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
@@ -9320,7 +9318,7 @@
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
@@ -9348,7 +9346,7 @@
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
@@ -9376,7 +9374,7 @@
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
@@ -9404,7 +9402,7 @@
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
@@ -9432,7 +9430,7 @@
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
       <c r="G273" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H273" s="1"/>
       <c r="I273" s="1"/>
@@ -9460,10 +9458,10 @@
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I274" s="1"/>
       <c r="J274" s="1"/>
@@ -9490,10 +9488,10 @@
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I275" s="1"/>
       <c r="J275" s="1"/>
@@ -9520,10 +9518,10 @@
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
@@ -9550,10 +9548,10 @@
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
       <c r="G277" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I277" s="1"/>
       <c r="J277" s="1"/>
@@ -9580,10 +9578,10 @@
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I278" s="1"/>
       <c r="J278" s="1"/>
@@ -9610,10 +9608,10 @@
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I279" s="1"/>
       <c r="J279" s="1"/>
@@ -9640,10 +9638,10 @@
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I280" s="1"/>
       <c r="J280" s="1"/>
@@ -9670,10 +9668,10 @@
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H281" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H281" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
@@ -9700,10 +9698,10 @@
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I282" s="1"/>
       <c r="J282" s="1"/>
@@ -9730,10 +9728,10 @@
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H283" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H283" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
@@ -9760,10 +9758,10 @@
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
       <c r="G284" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I284" s="1"/>
       <c r="J284" s="1"/>
@@ -9790,10 +9788,10 @@
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I285" s="1"/>
       <c r="J285" s="1"/>
@@ -9820,10 +9818,10 @@
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
@@ -9850,10 +9848,10 @@
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
       <c r="G287" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
@@ -9880,10 +9878,10 @@
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
       <c r="G288" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I288" s="1"/>
       <c r="J288" s="1"/>
@@ -9910,10 +9908,10 @@
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
       <c r="G289" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I289" s="1"/>
       <c r="J289" s="1"/>
@@ -9940,10 +9938,10 @@
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I290" s="1"/>
       <c r="J290" s="1"/>
@@ -9970,10 +9968,10 @@
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I291" s="1"/>
       <c r="J291" s="1"/>
@@ -10000,7 +9998,7 @@
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
       <c r="G292" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H292" s="1"/>
       <c r="I292" s="1"/>
@@ -10028,7 +10026,7 @@
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H293" s="1"/>
       <c r="I293" s="1"/>
@@ -10056,7 +10054,7 @@
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
@@ -10084,7 +10082,7 @@
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
       <c r="G295" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H295" s="1"/>
       <c r="I295" s="1"/>
@@ -10112,7 +10110,7 @@
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
       <c r="G296" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H296" s="1"/>
       <c r="I296" s="1"/>
@@ -10140,7 +10138,7 @@
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H297" s="1"/>
       <c r="I297" s="1"/>
@@ -10168,7 +10166,7 @@
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
       <c r="G298" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H298" s="1"/>
       <c r="I298" s="1"/>
@@ -10196,7 +10194,7 @@
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
       <c r="G299" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H299" s="1"/>
       <c r="I299" s="1"/>
@@ -10224,7 +10222,7 @@
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
       <c r="G300" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
@@ -10252,7 +10250,7 @@
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
       <c r="G301" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H301" s="1"/>
       <c r="I301" s="1"/>
@@ -10280,7 +10278,7 @@
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H302" s="1"/>
       <c r="I302" s="1"/>
@@ -10308,10 +10306,10 @@
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H303" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I303" s="1"/>
       <c r="J303" s="1"/>
@@ -10342,10 +10340,10 @@
         <v>2000</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
@@ -10376,10 +10374,10 @@
         <v>1983</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
@@ -10410,10 +10408,10 @@
         <v>2018</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
@@ -10444,10 +10442,10 @@
         <v>1999</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I307" s="1"/>
       <c r="J307" s="1"/>
@@ -10478,10 +10476,10 @@
         <v>2000</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -10508,10 +10506,10 @@
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I309" s="1"/>
       <c r="J309" s="1"/>
@@ -10538,10 +10536,10 @@
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H310" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H310" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I310" s="1"/>
       <c r="J310" s="1"/>
@@ -10572,10 +10570,10 @@
         <v>2747</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I311" s="1"/>
       <c r="J311" s="1"/>
@@ -10606,10 +10604,10 @@
         <v>2741</v>
       </c>
       <c r="G312" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H312" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H312" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I312" s="1"/>
       <c r="J312" s="1"/>
@@ -10640,10 +10638,10 @@
         <v>2743</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
@@ -10670,10 +10668,10 @@
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
@@ -10700,10 +10698,10 @@
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I315" s="1"/>
       <c r="J315" s="1"/>
@@ -10730,10 +10728,10 @@
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I316" s="1"/>
       <c r="J316" s="1"/>
@@ -10760,10 +10758,10 @@
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
@@ -10790,10 +10788,10 @@
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
       <c r="G318" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
@@ -10820,10 +10818,10 @@
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I319" s="1"/>
       <c r="J319" s="1"/>
@@ -10850,10 +10848,10 @@
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
@@ -10884,7 +10882,7 @@
         <v>2179</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H321" s="1"/>
       <c r="I321" s="1"/>
@@ -10916,7 +10914,7 @@
         <v>2362</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H322" s="1"/>
       <c r="I322" s="1"/>
@@ -10948,7 +10946,7 @@
         <v>2548</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H323" s="1"/>
       <c r="I323" s="1"/>
@@ -10976,7 +10974,7 @@
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
       <c r="G324" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H324" s="1"/>
       <c r="I324" s="1"/>
@@ -11004,7 +11002,7 @@
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
       <c r="G325" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H325" s="1"/>
       <c r="I325" s="1"/>
@@ -11032,7 +11030,7 @@
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
       <c r="G326" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H326" s="1"/>
       <c r="I326" s="1"/>
@@ -11060,7 +11058,7 @@
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
       <c r="G327" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H327" s="1"/>
       <c r="I327" s="1"/>
@@ -11088,7 +11086,7 @@
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H328" s="1"/>
       <c r="I328" s="1"/>
@@ -11116,7 +11114,7 @@
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
       <c r="G329" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H329" s="1"/>
       <c r="I329" s="1"/>
@@ -11144,7 +11142,7 @@
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
       <c r="G330" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H330" s="1"/>
       <c r="I330" s="1"/>
@@ -11172,7 +11170,7 @@
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
       <c r="G331" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H331" s="1"/>
       <c r="I331" s="1"/>
@@ -11200,10 +11198,10 @@
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H332" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I332" s="1"/>
       <c r="J332" s="1"/>
@@ -11230,10 +11228,10 @@
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I333" s="1"/>
       <c r="J333" s="1"/>
@@ -11260,10 +11258,10 @@
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
@@ -11290,10 +11288,10 @@
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I335" s="1"/>
       <c r="J335" s="1"/>
@@ -11320,10 +11318,10 @@
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H336" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
@@ -11350,10 +11348,10 @@
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
       <c r="G337" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
@@ -11380,10 +11378,10 @@
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
@@ -11410,10 +11408,10 @@
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H339" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H339" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
@@ -11440,10 +11438,10 @@
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I340" s="1"/>
       <c r="J340" s="1"/>
@@ -11470,10 +11468,10 @@
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H341" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H341" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
@@ -11500,10 +11498,10 @@
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
       <c r="G342" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I342" s="1"/>
       <c r="J342" s="1"/>
@@ -11530,10 +11528,10 @@
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
@@ -11560,10 +11558,10 @@
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
@@ -11590,10 +11588,10 @@
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
       <c r="G345" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
@@ -11620,10 +11618,10 @@
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
       <c r="G346" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
@@ -11650,10 +11648,10 @@
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I347" s="1"/>
       <c r="J347" s="1"/>
@@ -11680,10 +11678,10 @@
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
@@ -11710,10 +11708,10 @@
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I349" s="1"/>
       <c r="J349" s="1"/>
@@ -11740,7 +11738,7 @@
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
       <c r="G350" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H350" s="1"/>
       <c r="I350" s="1"/>
@@ -11768,7 +11766,7 @@
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
       <c r="G351" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H351" s="1"/>
       <c r="I351" s="1"/>
@@ -11796,7 +11794,7 @@
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
       <c r="G352" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
@@ -11824,7 +11822,7 @@
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
       <c r="G353" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
@@ -11852,7 +11850,7 @@
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
       <c r="G354" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
@@ -11880,7 +11878,7 @@
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
       <c r="G355" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
@@ -11908,7 +11906,7 @@
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
       <c r="G356" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H356" s="1"/>
       <c r="I356" s="1"/>
@@ -11936,7 +11934,7 @@
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H357" s="1"/>
       <c r="I357" s="1"/>
@@ -11964,7 +11962,7 @@
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H358" s="1"/>
       <c r="I358" s="1"/>
@@ -11992,7 +11990,7 @@
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H359" s="1"/>
       <c r="I359" s="1"/>
@@ -12020,7 +12018,7 @@
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
       <c r="G360" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H360" s="1"/>
       <c r="I360" s="1"/>
@@ -12048,10 +12046,10 @@
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H361" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
@@ -12078,10 +12076,10 @@
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
       <c r="G362" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
@@ -12108,10 +12106,10 @@
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
       <c r="G363" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
@@ -12138,10 +12136,10 @@
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
       <c r="G364" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
@@ -12168,10 +12166,10 @@
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H365" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
@@ -12198,10 +12196,10 @@
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H366" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
@@ -12228,10 +12226,10 @@
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
       <c r="G367" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
@@ -12258,10 +12256,10 @@
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
       <c r="G368" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H368" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H368" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
@@ -12288,10 +12286,10 @@
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H369" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
@@ -12318,10 +12316,10 @@
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
       <c r="G370" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H370" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H370" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
@@ -12348,10 +12346,10 @@
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
       <c r="G371" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
@@ -12378,10 +12376,10 @@
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
       <c r="G372" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
@@ -12408,10 +12406,10 @@
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
       <c r="G373" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
@@ -12438,10 +12436,10 @@
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
@@ -12468,10 +12466,10 @@
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
       <c r="G375" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
@@ -12498,10 +12496,10 @@
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
       <c r="G376" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
@@ -12528,10 +12526,10 @@
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
       <c r="G377" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H377" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
@@ -12558,10 +12556,10 @@
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
       <c r="G378" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H378" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I378" s="1"/>
       <c r="J378" s="1"/>
@@ -12588,7 +12586,7 @@
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H379" s="1"/>
       <c r="I379" s="1"/>
@@ -12616,7 +12614,7 @@
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
       <c r="G380" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H380" s="1"/>
       <c r="I380" s="1"/>
@@ -12644,7 +12642,7 @@
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
       <c r="G381" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H381" s="1"/>
       <c r="I381" s="1"/>
@@ -12672,7 +12670,7 @@
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
       <c r="G382" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H382" s="1"/>
       <c r="I382" s="1"/>
@@ -12700,7 +12698,7 @@
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
       <c r="G383" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H383" s="1"/>
       <c r="I383" s="1"/>
@@ -12728,7 +12726,7 @@
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
       <c r="G384" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H384" s="1"/>
       <c r="I384" s="1"/>
@@ -12756,7 +12754,7 @@
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
       <c r="G385" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H385" s="1"/>
       <c r="I385" s="1"/>
@@ -12784,7 +12782,7 @@
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
       <c r="G386" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H386" s="1"/>
       <c r="I386" s="1"/>
@@ -12812,7 +12810,7 @@
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
       <c r="G387" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H387" s="1"/>
       <c r="I387" s="1"/>
@@ -12840,7 +12838,7 @@
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
       <c r="G388" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H388" s="1"/>
       <c r="I388" s="1"/>
@@ -12868,7 +12866,7 @@
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
       <c r="G389" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H389" s="1"/>
       <c r="I389" s="1"/>
@@ -12896,10 +12894,10 @@
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H390" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I390" s="1"/>
       <c r="J390" s="1"/>
@@ -12926,10 +12924,10 @@
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
       <c r="G391" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I391" s="1"/>
       <c r="J391" s="1"/>
@@ -12956,10 +12954,10 @@
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I392" s="1"/>
       <c r="J392" s="1"/>
@@ -12986,10 +12984,10 @@
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
       <c r="G393" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I393" s="1"/>
       <c r="J393" s="1"/>
@@ -13016,10 +13014,10 @@
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H394" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I394" s="1"/>
       <c r="J394" s="1"/>
@@ -13046,10 +13044,10 @@
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I395" s="1"/>
       <c r="J395" s="1"/>
@@ -13076,10 +13074,10 @@
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I396" s="1"/>
       <c r="J396" s="1"/>
@@ -13106,10 +13104,10 @@
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
       <c r="G397" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H397" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H397" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I397" s="1"/>
       <c r="J397" s="1"/>
@@ -13136,10 +13134,10 @@
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
       <c r="G398" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I398" s="1"/>
       <c r="J398" s="1"/>
@@ -13166,10 +13164,10 @@
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
       <c r="G399" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H399" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H399" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I399" s="1"/>
       <c r="J399" s="1"/>
@@ -13196,10 +13194,10 @@
       <c r="E400" s="2"/>
       <c r="F400" s="2"/>
       <c r="G400" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I400" s="1"/>
       <c r="J400" s="1"/>
@@ -13226,10 +13224,10 @@
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
       <c r="G401" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I401" s="1"/>
       <c r="J401" s="1"/>
@@ -13256,10 +13254,10 @@
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
       <c r="G402" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H402" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I402" s="1"/>
       <c r="J402" s="1"/>
@@ -13286,10 +13284,10 @@
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
       <c r="G403" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I403" s="1"/>
       <c r="J403" s="1"/>
@@ -13316,10 +13314,10 @@
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
       <c r="G404" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I404" s="1"/>
       <c r="J404" s="1"/>
@@ -13346,10 +13344,10 @@
       <c r="E405" s="2"/>
       <c r="F405" s="2"/>
       <c r="G405" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I405" s="1"/>
       <c r="J405" s="1"/>
@@ -13376,10 +13374,10 @@
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
       <c r="G406" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I406" s="1"/>
       <c r="J406" s="1"/>
@@ -13406,10 +13404,10 @@
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
       <c r="G407" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H407" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I407" s="1"/>
       <c r="J407" s="1"/>
@@ -13436,7 +13434,7 @@
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
       <c r="G408" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H408" s="1"/>
       <c r="I408" s="1"/>
@@ -13464,7 +13462,7 @@
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
       <c r="G409" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H409" s="1"/>
       <c r="I409" s="1"/>
@@ -13492,7 +13490,7 @@
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
       <c r="G410" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H410" s="1"/>
       <c r="I410" s="1"/>
@@ -13520,7 +13518,7 @@
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
       <c r="G411" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
@@ -13548,7 +13546,7 @@
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H412" s="1"/>
       <c r="I412" s="1"/>
@@ -13576,7 +13574,7 @@
       <c r="E413" s="2"/>
       <c r="F413" s="2"/>
       <c r="G413" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H413" s="1"/>
       <c r="I413" s="1"/>
@@ -13604,7 +13602,7 @@
       <c r="E414" s="2"/>
       <c r="F414" s="2"/>
       <c r="G414" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H414" s="1"/>
       <c r="I414" s="1"/>
@@ -13632,7 +13630,7 @@
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
@@ -13660,7 +13658,7 @@
       <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
@@ -13688,7 +13686,7 @@
       <c r="E417" s="2"/>
       <c r="F417" s="2"/>
       <c r="G417" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H417" s="1"/>
       <c r="I417" s="1"/>
@@ -13716,7 +13714,7 @@
       <c r="E418" s="2"/>
       <c r="F418" s="2"/>
       <c r="G418" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H418" s="1"/>
       <c r="I418" s="1"/>
@@ -13744,10 +13742,10 @@
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I419" s="1"/>
       <c r="J419" s="1"/>
@@ -13774,10 +13772,10 @@
       <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H420" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I420" s="1"/>
       <c r="J420" s="1"/>
@@ -13804,10 +13802,10 @@
       <c r="E421" s="2"/>
       <c r="F421" s="2"/>
       <c r="G421" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I421" s="1"/>
       <c r="J421" s="1"/>
@@ -13834,10 +13832,10 @@
       <c r="E422" s="2"/>
       <c r="F422" s="2"/>
       <c r="G422" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I422" s="1"/>
       <c r="J422" s="1"/>
@@ -13864,10 +13862,10 @@
       <c r="E423" s="2"/>
       <c r="F423" s="2"/>
       <c r="G423" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I423" s="1"/>
       <c r="J423" s="1"/>
@@ -13894,10 +13892,10 @@
       <c r="E424" s="2"/>
       <c r="F424" s="2"/>
       <c r="G424" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I424" s="1"/>
       <c r="J424" s="1"/>
@@ -13924,10 +13922,10 @@
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
       <c r="G425" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I425" s="1"/>
       <c r="J425" s="1"/>
@@ -13954,10 +13952,10 @@
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
       <c r="G426" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H426" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H426" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I426" s="1"/>
       <c r="J426" s="1"/>
@@ -13984,10 +13982,10 @@
       <c r="E427" s="2"/>
       <c r="F427" s="2"/>
       <c r="G427" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I427" s="1"/>
       <c r="J427" s="1"/>
@@ -14014,10 +14012,10 @@
       <c r="E428" s="2"/>
       <c r="F428" s="2"/>
       <c r="G428" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H428" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H428" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I428" s="1"/>
       <c r="J428" s="1"/>
@@ -14044,10 +14042,10 @@
       <c r="E429" s="2"/>
       <c r="F429" s="2"/>
       <c r="G429" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
@@ -14074,10 +14072,10 @@
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
       <c r="G430" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
@@ -14104,10 +14102,10 @@
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
       <c r="G431" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I431" s="1"/>
       <c r="J431" s="1"/>
@@ -14134,10 +14132,10 @@
       <c r="E432" s="2"/>
       <c r="F432" s="2"/>
       <c r="G432" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I432" s="1"/>
       <c r="J432" s="1"/>
@@ -14164,10 +14162,10 @@
       <c r="E433" s="2"/>
       <c r="F433" s="2"/>
       <c r="G433" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I433" s="1"/>
       <c r="J433" s="1"/>
@@ -14194,10 +14192,10 @@
       <c r="E434" s="2"/>
       <c r="F434" s="2"/>
       <c r="G434" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I434" s="1"/>
       <c r="J434" s="1"/>
@@ -14224,10 +14222,10 @@
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I435" s="1"/>
       <c r="J435" s="1"/>
@@ -14254,10 +14252,10 @@
       <c r="E436" s="1"/>
       <c r="F436" s="1"/>
       <c r="G436" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I436" s="1"/>
       <c r="J436" s="1"/>
@@ -14284,7 +14282,7 @@
       <c r="E437" s="2"/>
       <c r="F437" s="2"/>
       <c r="G437" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H437" s="1"/>
       <c r="I437" s="1"/>
@@ -14312,7 +14310,7 @@
       <c r="E438" s="2"/>
       <c r="F438" s="2"/>
       <c r="G438" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H438" s="1"/>
       <c r="I438" s="1"/>
@@ -14340,7 +14338,7 @@
       <c r="E439" s="2"/>
       <c r="F439" s="2"/>
       <c r="G439" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
@@ -14368,7 +14366,7 @@
       <c r="E440" s="2"/>
       <c r="F440" s="2"/>
       <c r="G440" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H440" s="1"/>
       <c r="I440" s="1"/>
@@ -14396,7 +14394,7 @@
       <c r="E441" s="2"/>
       <c r="F441" s="2"/>
       <c r="G441" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H441" s="1"/>
       <c r="I441" s="1"/>
@@ -14424,7 +14422,7 @@
       <c r="E442" s="2"/>
       <c r="F442" s="2"/>
       <c r="G442" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H442" s="1"/>
       <c r="I442" s="1"/>
@@ -14452,7 +14450,7 @@
       <c r="E443" s="2"/>
       <c r="F443" s="2"/>
       <c r="G443" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H443" s="1"/>
       <c r="I443" s="1"/>
@@ -14480,7 +14478,7 @@
       <c r="E444" s="2"/>
       <c r="F444" s="2"/>
       <c r="G444" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H444" s="1"/>
       <c r="I444" s="1"/>
@@ -14508,7 +14506,7 @@
       <c r="E445" s="2"/>
       <c r="F445" s="2"/>
       <c r="G445" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H445" s="1"/>
       <c r="I445" s="1"/>
@@ -14536,7 +14534,7 @@
       <c r="E446" s="2"/>
       <c r="F446" s="2"/>
       <c r="G446" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H446" s="1"/>
       <c r="I446" s="1"/>
@@ -14564,7 +14562,7 @@
       <c r="E447" s="2"/>
       <c r="F447" s="2"/>
       <c r="G447" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H447" s="1"/>
       <c r="I447" s="1"/>
@@ -14592,10 +14590,10 @@
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H448" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I448" s="1"/>
       <c r="J448" s="1"/>
@@ -14622,10 +14620,10 @@
       <c r="E449" s="2"/>
       <c r="F449" s="2"/>
       <c r="G449" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I449" s="1"/>
       <c r="J449" s="1"/>
@@ -14652,10 +14650,10 @@
       <c r="E450" s="2"/>
       <c r="F450" s="2"/>
       <c r="G450" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I450" s="1"/>
       <c r="J450" s="1"/>
@@ -14682,10 +14680,10 @@
       <c r="E451" s="2"/>
       <c r="F451" s="2"/>
       <c r="G451" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I451" s="1"/>
       <c r="J451" s="1"/>
@@ -14712,10 +14710,10 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H452" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I452" s="1"/>
       <c r="J452" s="1"/>
@@ -14742,10 +14740,10 @@
       <c r="E453" s="2"/>
       <c r="F453" s="2"/>
       <c r="G453" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I453" s="1"/>
       <c r="J453" s="1"/>
@@ -14772,10 +14770,10 @@
       <c r="E454" s="1"/>
       <c r="F454" s="1"/>
       <c r="G454" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I454" s="1"/>
       <c r="J454" s="1"/>
@@ -14802,10 +14800,10 @@
       <c r="E455" s="1"/>
       <c r="F455" s="1"/>
       <c r="G455" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H455" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H455" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I455" s="1"/>
       <c r="J455" s="1"/>
@@ -14832,10 +14830,10 @@
       <c r="E456" s="2"/>
       <c r="F456" s="2"/>
       <c r="G456" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I456" s="1"/>
       <c r="J456" s="1"/>
@@ -14862,10 +14860,10 @@
       <c r="E457" s="2"/>
       <c r="F457" s="2"/>
       <c r="G457" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H457" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H457" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I457" s="1"/>
       <c r="J457" s="1"/>
@@ -14892,10 +14890,10 @@
       <c r="E458" s="2"/>
       <c r="F458" s="2"/>
       <c r="G458" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I458" s="1"/>
       <c r="J458" s="1"/>
@@ -14922,10 +14920,10 @@
       <c r="E459" s="1"/>
       <c r="F459" s="1"/>
       <c r="G459" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I459" s="1"/>
       <c r="J459" s="1"/>
@@ -14952,10 +14950,10 @@
       <c r="E460" s="1"/>
       <c r="F460" s="1"/>
       <c r="G460" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I460" s="1"/>
       <c r="J460" s="1"/>
@@ -14982,10 +14980,10 @@
       <c r="E461" s="2"/>
       <c r="F461" s="2"/>
       <c r="G461" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I461" s="1"/>
       <c r="J461" s="1"/>
@@ -15012,10 +15010,10 @@
       <c r="E462" s="2"/>
       <c r="F462" s="2"/>
       <c r="G462" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I462" s="1"/>
       <c r="J462" s="1"/>
@@ -15042,10 +15040,10 @@
       <c r="E463" s="2"/>
       <c r="F463" s="2"/>
       <c r="G463" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I463" s="1"/>
       <c r="J463" s="1"/>
@@ -15072,10 +15070,10 @@
       <c r="E464" s="1"/>
       <c r="F464" s="1"/>
       <c r="G464" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I464" s="1"/>
       <c r="J464" s="1"/>
@@ -15102,10 +15100,10 @@
       <c r="E465" s="1"/>
       <c r="F465" s="1"/>
       <c r="G465" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I465" s="1"/>
       <c r="J465" s="1"/>
@@ -15132,7 +15130,7 @@
       <c r="E466" s="2"/>
       <c r="F466" s="2"/>
       <c r="G466" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H466" s="1"/>
       <c r="I466" s="1"/>
@@ -15160,7 +15158,7 @@
       <c r="E467" s="2"/>
       <c r="F467" s="2"/>
       <c r="G467" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H467" s="1"/>
       <c r="I467" s="1"/>
@@ -15188,7 +15186,7 @@
       <c r="E468" s="2"/>
       <c r="F468" s="2"/>
       <c r="G468" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H468" s="1"/>
       <c r="I468" s="1"/>
@@ -15216,7 +15214,7 @@
       <c r="E469" s="2"/>
       <c r="F469" s="2"/>
       <c r="G469" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H469" s="1"/>
       <c r="I469" s="1"/>
@@ -15244,7 +15242,7 @@
       <c r="E470" s="2"/>
       <c r="F470" s="2"/>
       <c r="G470" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H470" s="1"/>
       <c r="I470" s="1"/>
@@ -15272,7 +15270,7 @@
       <c r="E471" s="2"/>
       <c r="F471" s="2"/>
       <c r="G471" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H471" s="1"/>
       <c r="I471" s="1"/>
@@ -15300,7 +15298,7 @@
       <c r="E472" s="2"/>
       <c r="F472" s="2"/>
       <c r="G472" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H472" s="1"/>
       <c r="I472" s="1"/>
@@ -15328,7 +15326,7 @@
       <c r="E473" s="2"/>
       <c r="F473" s="2"/>
       <c r="G473" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H473" s="1"/>
       <c r="I473" s="1"/>
@@ -15356,7 +15354,7 @@
       <c r="E474" s="2"/>
       <c r="F474" s="2"/>
       <c r="G474" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H474" s="1"/>
       <c r="I474" s="1"/>
@@ -15384,7 +15382,7 @@
       <c r="E475" s="2"/>
       <c r="F475" s="2"/>
       <c r="G475" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H475" s="1"/>
       <c r="I475" s="1"/>
@@ -15412,7 +15410,7 @@
       <c r="E476" s="2"/>
       <c r="F476" s="2"/>
       <c r="G476" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H476" s="1"/>
       <c r="I476" s="1"/>
@@ -15440,10 +15438,10 @@
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
       <c r="G477" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H477" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I477" s="1"/>
       <c r="J477" s="1"/>
@@ -15470,10 +15468,10 @@
       <c r="E478" s="2"/>
       <c r="F478" s="2"/>
       <c r="G478" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I478" s="1"/>
       <c r="J478" s="1"/>
@@ -15500,10 +15498,10 @@
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I479" s="1"/>
       <c r="J479" s="1"/>
@@ -15530,10 +15528,10 @@
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I480" s="1"/>
       <c r="J480" s="1"/>
@@ -15560,10 +15558,10 @@
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H481" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I481" s="1"/>
       <c r="J481" s="1"/>
@@ -15590,10 +15588,10 @@
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I482" s="1"/>
       <c r="J482" s="1"/>
@@ -15620,10 +15618,10 @@
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
       <c r="G483" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I483" s="1"/>
       <c r="J483" s="1"/>
@@ -15650,10 +15648,10 @@
       <c r="E484" s="1"/>
       <c r="F484" s="1"/>
       <c r="G484" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H484" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H484" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I484" s="1"/>
       <c r="J484" s="1"/>
@@ -15680,10 +15678,10 @@
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I485" s="1"/>
       <c r="J485" s="1"/>
@@ -15710,10 +15708,10 @@
       <c r="E486" s="2"/>
       <c r="F486" s="2"/>
       <c r="G486" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H486" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H486" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I486" s="1"/>
       <c r="J486" s="1"/>
@@ -15740,10 +15738,10 @@
       <c r="E487" s="2"/>
       <c r="F487" s="2"/>
       <c r="G487" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I487" s="1"/>
       <c r="J487" s="1"/>
@@ -15770,10 +15768,10 @@
       <c r="E488" s="1"/>
       <c r="F488" s="1"/>
       <c r="G488" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I488" s="1"/>
       <c r="J488" s="1"/>
@@ -15800,10 +15798,10 @@
       <c r="E489" s="1"/>
       <c r="F489" s="1"/>
       <c r="G489" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I489" s="1"/>
       <c r="J489" s="1"/>
@@ -15830,10 +15828,10 @@
       <c r="E490" s="2"/>
       <c r="F490" s="2"/>
       <c r="G490" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I490" s="1"/>
       <c r="J490" s="1"/>
@@ -15860,10 +15858,10 @@
       <c r="E491" s="2"/>
       <c r="F491" s="2"/>
       <c r="G491" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I491" s="1"/>
       <c r="J491" s="1"/>
@@ -15890,10 +15888,10 @@
       <c r="E492" s="2"/>
       <c r="F492" s="2"/>
       <c r="G492" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I492" s="1"/>
       <c r="J492" s="1"/>
@@ -15920,10 +15918,10 @@
       <c r="E493" s="1"/>
       <c r="F493" s="1"/>
       <c r="G493" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I493" s="1"/>
       <c r="J493" s="1"/>
@@ -15950,10 +15948,10 @@
       <c r="E494" s="1"/>
       <c r="F494" s="1"/>
       <c r="G494" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I494" s="1"/>
       <c r="J494" s="1"/>
@@ -15980,7 +15978,7 @@
       <c r="E495" s="2"/>
       <c r="F495" s="2"/>
       <c r="G495" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H495" s="1"/>
       <c r="I495" s="1"/>
@@ -16008,7 +16006,7 @@
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H496" s="1"/>
       <c r="I496" s="1"/>
@@ -16036,7 +16034,7 @@
       <c r="E497" s="2"/>
       <c r="F497" s="2"/>
       <c r="G497" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H497" s="1"/>
       <c r="I497" s="1"/>
@@ -16064,7 +16062,7 @@
       <c r="E498" s="2"/>
       <c r="F498" s="2"/>
       <c r="G498" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H498" s="1"/>
       <c r="I498" s="1"/>
@@ -16092,7 +16090,7 @@
       <c r="E499" s="2"/>
       <c r="F499" s="2"/>
       <c r="G499" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H499" s="1"/>
       <c r="I499" s="1"/>
@@ -16120,7 +16118,7 @@
       <c r="E500" s="2"/>
       <c r="F500" s="2"/>
       <c r="G500" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H500" s="1"/>
       <c r="I500" s="1"/>
@@ -16148,7 +16146,7 @@
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H501" s="1"/>
       <c r="I501" s="1"/>
@@ -16176,7 +16174,7 @@
       <c r="E502" s="2"/>
       <c r="F502" s="2"/>
       <c r="G502" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H502" s="1"/>
       <c r="I502" s="1"/>
@@ -16204,7 +16202,7 @@
       <c r="E503" s="2"/>
       <c r="F503" s="2"/>
       <c r="G503" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H503" s="1"/>
       <c r="I503" s="1"/>
@@ -16232,7 +16230,7 @@
       <c r="E504" s="2"/>
       <c r="F504" s="2"/>
       <c r="G504" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H504" s="1"/>
       <c r="I504" s="1"/>
@@ -16260,7 +16258,7 @@
       <c r="E505" s="2"/>
       <c r="F505" s="2"/>
       <c r="G505" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H505" s="1"/>
       <c r="I505" s="1"/>
@@ -16288,10 +16286,10 @@
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
       <c r="G506" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H506" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I506" s="1"/>
       <c r="J506" s="1"/>
@@ -16318,10 +16316,10 @@
       <c r="E507" s="2"/>
       <c r="F507" s="2"/>
       <c r="G507" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H507" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I507" s="1"/>
       <c r="J507" s="1"/>
@@ -16348,10 +16346,10 @@
       <c r="E508" s="2"/>
       <c r="F508" s="2"/>
       <c r="G508" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I508" s="1"/>
       <c r="J508" s="1"/>
@@ -16378,10 +16376,10 @@
       <c r="E509" s="2"/>
       <c r="F509" s="2"/>
       <c r="G509" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I509" s="1"/>
       <c r="J509" s="1"/>
@@ -16408,10 +16406,10 @@
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I510" s="1"/>
       <c r="J510" s="1"/>
@@ -16438,10 +16436,10 @@
       <c r="E511" s="2"/>
       <c r="F511" s="2"/>
       <c r="G511" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I511" s="1"/>
       <c r="J511" s="1"/>
@@ -16468,10 +16466,10 @@
       <c r="E512" s="1"/>
       <c r="F512" s="1"/>
       <c r="G512" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I512" s="1"/>
       <c r="J512" s="1"/>
@@ -16498,10 +16496,10 @@
       <c r="E513" s="1"/>
       <c r="F513" s="1"/>
       <c r="G513" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H513" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H513" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I513" s="1"/>
       <c r="J513" s="1"/>
@@ -16528,10 +16526,10 @@
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I514" s="1"/>
       <c r="J514" s="1"/>
@@ -16558,10 +16556,10 @@
       <c r="E515" s="2"/>
       <c r="F515" s="2"/>
       <c r="G515" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H515" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H515" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I515" s="1"/>
       <c r="J515" s="1"/>
@@ -16588,10 +16586,10 @@
       <c r="E516" s="2"/>
       <c r="F516" s="2"/>
       <c r="G516" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I516" s="1"/>
       <c r="J516" s="1"/>
@@ -16618,10 +16616,10 @@
       <c r="E517" s="1"/>
       <c r="F517" s="1"/>
       <c r="G517" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I517" s="1"/>
       <c r="J517" s="1"/>
@@ -16648,10 +16646,10 @@
       <c r="E518" s="1"/>
       <c r="F518" s="1"/>
       <c r="G518" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I518" s="1"/>
       <c r="J518" s="1"/>
@@ -16678,10 +16676,10 @@
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I519" s="1"/>
       <c r="J519" s="1"/>
@@ -16708,10 +16706,10 @@
       <c r="E520" s="2"/>
       <c r="F520" s="2"/>
       <c r="G520" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I520" s="1"/>
       <c r="J520" s="1"/>
@@ -16738,10 +16736,10 @@
       <c r="E521" s="2"/>
       <c r="F521" s="2"/>
       <c r="G521" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I521" s="1"/>
       <c r="J521" s="1"/>
@@ -16768,10 +16766,10 @@
       <c r="E522" s="1"/>
       <c r="F522" s="1"/>
       <c r="G522" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I522" s="1"/>
       <c r="J522" s="1"/>
@@ -16798,10 +16796,10 @@
       <c r="E523" s="1"/>
       <c r="F523" s="1"/>
       <c r="G523" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I523" s="1"/>
       <c r="J523" s="1"/>
@@ -16828,7 +16826,7 @@
       <c r="E524" s="2"/>
       <c r="F524" s="2"/>
       <c r="G524" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H524" s="1"/>
       <c r="I524" s="1"/>
@@ -16856,7 +16854,7 @@
       <c r="E525" s="2"/>
       <c r="F525" s="2"/>
       <c r="G525" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H525" s="1"/>
       <c r="I525" s="1"/>
@@ -16884,7 +16882,7 @@
       <c r="E526" s="2"/>
       <c r="F526" s="2"/>
       <c r="G526" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H526" s="1"/>
       <c r="I526" s="1"/>
@@ -16912,7 +16910,7 @@
       <c r="E527" s="2"/>
       <c r="F527" s="2"/>
       <c r="G527" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H527" s="1"/>
       <c r="I527" s="1"/>
@@ -16940,7 +16938,7 @@
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H528" s="1"/>
       <c r="I528" s="1"/>
@@ -16968,7 +16966,7 @@
       <c r="E529" s="2"/>
       <c r="F529" s="2"/>
       <c r="G529" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H529" s="1"/>
       <c r="I529" s="1"/>
@@ -16996,7 +16994,7 @@
       <c r="E530" s="2"/>
       <c r="F530" s="2"/>
       <c r="G530" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H530" s="1"/>
       <c r="I530" s="1"/>
@@ -17024,7 +17022,7 @@
       <c r="E531" s="2"/>
       <c r="F531" s="2"/>
       <c r="G531" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H531" s="1"/>
       <c r="I531" s="1"/>
@@ -17052,7 +17050,7 @@
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H532" s="1"/>
       <c r="I532" s="1"/>
@@ -17080,7 +17078,7 @@
       <c r="E533" s="2"/>
       <c r="F533" s="2"/>
       <c r="G533" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H533" s="1"/>
       <c r="I533" s="1"/>
@@ -17108,7 +17106,7 @@
       <c r="E534" s="2"/>
       <c r="F534" s="2"/>
       <c r="G534" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H534" s="1"/>
       <c r="I534" s="1"/>
@@ -17136,10 +17134,10 @@
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
       <c r="G535" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H535" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I535" s="1"/>
       <c r="J535" s="1"/>
@@ -17166,10 +17164,10 @@
       <c r="E536" s="2"/>
       <c r="F536" s="2"/>
       <c r="G536" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H536" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I536" s="1"/>
       <c r="J536" s="1"/>
@@ -17196,10 +17194,10 @@
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I537" s="1"/>
       <c r="J537" s="1"/>
@@ -17226,10 +17224,10 @@
       <c r="E538" s="2"/>
       <c r="F538" s="2"/>
       <c r="G538" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I538" s="1"/>
       <c r="J538" s="1"/>
@@ -17256,10 +17254,10 @@
       <c r="E539" s="2"/>
       <c r="F539" s="2"/>
       <c r="G539" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H539" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I539" s="1"/>
       <c r="J539" s="1"/>
@@ -17286,10 +17284,10 @@
       <c r="E540" s="2"/>
       <c r="F540" s="2"/>
       <c r="G540" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H540" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I540" s="1"/>
       <c r="J540" s="1"/>
@@ -17316,10 +17314,10 @@
       <c r="E541" s="1"/>
       <c r="F541" s="1"/>
       <c r="G541" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H541" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I541" s="1"/>
       <c r="J541" s="1"/>
@@ -17346,10 +17344,10 @@
       <c r="E542" s="1"/>
       <c r="F542" s="1"/>
       <c r="G542" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H542" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H542" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I542" s="1"/>
       <c r="J542" s="1"/>
@@ -17376,10 +17374,10 @@
       <c r="E543" s="2"/>
       <c r="F543" s="2"/>
       <c r="G543" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H543" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I543" s="1"/>
       <c r="J543" s="1"/>
@@ -17406,10 +17404,10 @@
       <c r="E544" s="2"/>
       <c r="F544" s="2"/>
       <c r="G544" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H544" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H544" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I544" s="1"/>
       <c r="J544" s="1"/>
@@ -17436,10 +17434,10 @@
       <c r="E545" s="2"/>
       <c r="F545" s="2"/>
       <c r="G545" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H545" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I545" s="1"/>
       <c r="J545" s="1"/>
@@ -17466,10 +17464,10 @@
       <c r="E546" s="1"/>
       <c r="F546" s="1"/>
       <c r="G546" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H546" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I546" s="1"/>
       <c r="J546" s="1"/>
@@ -17496,10 +17494,10 @@
       <c r="E547" s="1"/>
       <c r="F547" s="1"/>
       <c r="G547" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H547" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I547" s="1"/>
       <c r="J547" s="1"/>
@@ -17526,10 +17524,10 @@
       <c r="E548" s="2"/>
       <c r="F548" s="2"/>
       <c r="G548" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I548" s="1"/>
       <c r="J548" s="1"/>
@@ -17556,10 +17554,10 @@
       <c r="E549" s="2"/>
       <c r="F549" s="2"/>
       <c r="G549" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I549" s="1"/>
       <c r="J549" s="1"/>
@@ -17586,10 +17584,10 @@
       <c r="E550" s="2"/>
       <c r="F550" s="2"/>
       <c r="G550" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I550" s="1"/>
       <c r="J550" s="1"/>
@@ -17616,10 +17614,10 @@
       <c r="E551" s="1"/>
       <c r="F551" s="1"/>
       <c r="G551" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I551" s="1"/>
       <c r="J551" s="1"/>
@@ -17646,10 +17644,10 @@
       <c r="E552" s="1"/>
       <c r="F552" s="1"/>
       <c r="G552" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H552" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I552" s="1"/>
       <c r="J552" s="1"/>
@@ -17676,7 +17674,7 @@
       <c r="E553" s="2"/>
       <c r="F553" s="2"/>
       <c r="G553" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H553" s="1"/>
       <c r="I553" s="1"/>
@@ -17704,7 +17702,7 @@
       <c r="E554" s="2"/>
       <c r="F554" s="2"/>
       <c r="G554" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H554" s="1"/>
       <c r="I554" s="1"/>
@@ -17732,7 +17730,7 @@
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H555" s="1"/>
       <c r="I555" s="1"/>
@@ -17760,7 +17758,7 @@
       <c r="E556" s="2"/>
       <c r="F556" s="2"/>
       <c r="G556" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H556" s="1"/>
       <c r="I556" s="1"/>
@@ -17788,7 +17786,7 @@
       <c r="E557" s="2"/>
       <c r="F557" s="2"/>
       <c r="G557" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H557" s="1"/>
       <c r="I557" s="1"/>
@@ -17816,7 +17814,7 @@
       <c r="E558" s="2"/>
       <c r="F558" s="2"/>
       <c r="G558" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H558" s="1"/>
       <c r="I558" s="1"/>
@@ -17844,7 +17842,7 @@
       <c r="E559" s="2"/>
       <c r="F559" s="2"/>
       <c r="G559" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H559" s="1"/>
       <c r="I559" s="1"/>
@@ -17872,7 +17870,7 @@
       <c r="E560" s="2"/>
       <c r="F560" s="2"/>
       <c r="G560" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H560" s="1"/>
       <c r="I560" s="1"/>
@@ -17900,7 +17898,7 @@
       <c r="E561" s="2"/>
       <c r="F561" s="2"/>
       <c r="G561" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H561" s="1"/>
       <c r="I561" s="1"/>
@@ -17928,7 +17926,7 @@
       <c r="E562" s="2"/>
       <c r="F562" s="2"/>
       <c r="G562" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H562" s="1"/>
       <c r="I562" s="1"/>
@@ -17956,7 +17954,7 @@
       <c r="E563" s="2"/>
       <c r="F563" s="2"/>
       <c r="G563" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H563" s="1"/>
       <c r="I563" s="1"/>
@@ -17984,10 +17982,10 @@
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
       <c r="G564" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H564" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I564" s="1"/>
       <c r="J564" s="1"/>
@@ -18014,10 +18012,10 @@
       <c r="E565" s="2"/>
       <c r="F565" s="2"/>
       <c r="G565" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H565" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I565" s="1"/>
       <c r="J565" s="1"/>
@@ -18044,10 +18042,10 @@
       <c r="E566" s="2"/>
       <c r="F566" s="2"/>
       <c r="G566" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I566" s="1"/>
       <c r="J566" s="1"/>
@@ -18074,10 +18072,10 @@
       <c r="E567" s="2"/>
       <c r="F567" s="2"/>
       <c r="G567" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I567" s="1"/>
       <c r="J567" s="1"/>
@@ -18104,10 +18102,10 @@
       <c r="E568" s="2"/>
       <c r="F568" s="2"/>
       <c r="G568" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H568" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I568" s="1"/>
       <c r="J568" s="1"/>
@@ -18134,10 +18132,10 @@
       <c r="E569" s="2"/>
       <c r="F569" s="2"/>
       <c r="G569" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H569" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I569" s="1"/>
       <c r="J569" s="1"/>
@@ -18164,10 +18162,10 @@
       <c r="E570" s="1"/>
       <c r="F570" s="1"/>
       <c r="G570" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H570" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I570" s="1"/>
       <c r="J570" s="1"/>
@@ -18194,10 +18192,10 @@
       <c r="E571" s="1"/>
       <c r="F571" s="1"/>
       <c r="G571" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H571" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H571" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I571" s="1"/>
       <c r="J571" s="1"/>
@@ -18224,10 +18222,10 @@
       <c r="E572" s="2"/>
       <c r="F572" s="2"/>
       <c r="G572" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H572" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I572" s="1"/>
       <c r="J572" s="1"/>
@@ -18254,10 +18252,10 @@
       <c r="E573" s="2"/>
       <c r="F573" s="2"/>
       <c r="G573" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H573" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H573" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I573" s="1"/>
       <c r="J573" s="1"/>
@@ -18284,10 +18282,10 @@
       <c r="E574" s="2"/>
       <c r="F574" s="2"/>
       <c r="G574" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I574" s="1"/>
       <c r="J574" s="1"/>
@@ -18314,10 +18312,10 @@
       <c r="E575" s="1"/>
       <c r="F575" s="1"/>
       <c r="G575" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H575" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="I575" s="1"/>
       <c r="J575" s="1"/>
@@ -18344,10 +18342,10 @@
       <c r="E576" s="1"/>
       <c r="F576" s="1"/>
       <c r="G576" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H576" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I576" s="1"/>
       <c r="J576" s="1"/>
@@ -18374,10 +18372,10 @@
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H577" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I577" s="1"/>
       <c r="J577" s="1"/>
@@ -18404,10 +18402,10 @@
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H578" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I578" s="1"/>
       <c r="J578" s="1"/>
@@ -18434,10 +18432,10 @@
       <c r="E579" s="2"/>
       <c r="F579" s="2"/>
       <c r="G579" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H579" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I579" s="1"/>
       <c r="J579" s="1"/>
@@ -18464,10 +18462,10 @@
       <c r="E580" s="1"/>
       <c r="F580" s="1"/>
       <c r="G580" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H580" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I580" s="1"/>
       <c r="J580" s="1"/>
@@ -18494,10 +18492,10 @@
       <c r="E581" s="1"/>
       <c r="F581" s="1"/>
       <c r="G581" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H581" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I581" s="1"/>
       <c r="J581" s="1"/>
@@ -18524,7 +18522,7 @@
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H582" s="1"/>
       <c r="I582" s="1"/>
@@ -18552,7 +18550,7 @@
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H583" s="1"/>
       <c r="I583" s="1"/>
@@ -18580,7 +18578,7 @@
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H584" s="1"/>
       <c r="I584" s="1"/>
@@ -18608,7 +18606,7 @@
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
       <c r="G585" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H585" s="1"/>
       <c r="I585" s="1"/>
@@ -18636,7 +18634,7 @@
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
       <c r="G586" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H586" s="1"/>
       <c r="I586" s="1"/>
@@ -18664,7 +18662,7 @@
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
       <c r="G587" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H587" s="1"/>
       <c r="I587" s="1"/>
@@ -18692,7 +18690,7 @@
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
       <c r="G588" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H588" s="1"/>
       <c r="I588" s="1"/>
@@ -18720,7 +18718,7 @@
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
       <c r="G589" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H589" s="1"/>
       <c r="I589" s="1"/>
@@ -18748,7 +18746,7 @@
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
       <c r="G590" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H590" s="1"/>
       <c r="I590" s="1"/>
@@ -18776,7 +18774,7 @@
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
       <c r="G591" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H591" s="1"/>
       <c r="I591" s="1"/>
@@ -18804,7 +18802,7 @@
       <c r="E592" s="2"/>
       <c r="F592" s="2"/>
       <c r="G592" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H592" s="1"/>
       <c r="I592" s="1"/>

--- a/awim/cal slayer 0.5 zoom.xlsx
+++ b/awim/cal slayer 0.5 zoom.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/640dce341da437cb/02 Time v3 physical Clock/Time v3 Clock camera and image processing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F30152-0561-4676-BE96-85966EAA726C}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="13_ncr:40009_{B2970093-D86E-46D6-A84B-1B4BF93138CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA200542-27ED-4399-98F9-A67D00598F21}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,12 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="51">
   <si>
-    <t>rec_x</t>
-  </si>
-  <si>
-    <t>rec_y</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -38,12 +32,6 @@
   </si>
   <si>
     <t>out2</t>
-  </si>
-  <si>
-    <t>px_x</t>
-  </si>
-  <si>
-    <t>px_y</t>
   </si>
   <si>
     <t>camera_name</t>
@@ -148,31 +136,43 @@
     <t>LB</t>
   </si>
   <si>
-    <t>target_pos_xysph_relaim</t>
+    <t>xang_sect</t>
   </si>
   <si>
-    <t>xsph_sect</t>
+    <t>yang_sect</t>
   </si>
   <si>
-    <t>ysph_sect</t>
+    <t>xang_rel</t>
   </si>
   <si>
-    <t>xsph_rel</t>
+    <t>yang_rel</t>
   </si>
   <si>
-    <t>ysph_rel</t>
+    <t>x_rec</t>
   </si>
   <si>
-    <t>xsph_total</t>
+    <t>y_rec</t>
   </si>
   <si>
-    <t>ysph_total</t>
+    <t>xang_total</t>
   </si>
   <si>
-    <t>xsph</t>
+    <t>yang_total</t>
   </si>
   <si>
-    <t>ysph</t>
+    <t>x_px</t>
+  </si>
+  <si>
+    <t>y_px</t>
+  </si>
+  <si>
+    <t>xang</t>
+  </si>
+  <si>
+    <t>yang</t>
+  </si>
+  <si>
+    <t>target_pos_xyangs_relaim</t>
   </si>
 </sst>
 </file>
@@ -1064,52 +1064,52 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="L1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -1120,10 +1120,10 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1146,7 +1146,7 @@
         <v>3000</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1166,10 +1166,10 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -1188,7 +1188,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1208,7 +1208,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="1"/>
@@ -1232,7 +1232,7 @@
         <v>2250</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1252,10 +1252,10 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1274,10 +1274,10 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1296,10 +1296,10 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1318,7 +1318,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -1352,10 +1352,10 @@
         <v>-1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1382,10 +1382,10 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1416,10 +1416,10 @@
         <v>2004</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1450,10 +1450,10 @@
         <v>1989</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1484,10 +1484,10 @@
         <v>2020</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1518,10 +1518,10 @@
         <v>2004</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1552,10 +1552,10 @@
         <v>2004</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1582,10 +1582,10 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1612,10 +1612,10 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1646,10 +1646,10 @@
         <v>2654</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1680,10 +1680,10 @@
         <v>2653</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1714,10 +1714,10 @@
         <v>2653</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1744,10 +1744,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1774,10 +1774,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>1991</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1842,10 +1842,10 @@
         <v>2022</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1876,10 +1876,10 @@
         <v>2006</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1906,10 +1906,10 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1936,10 +1936,10 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -1970,7 +1970,7 @@
         <v>2160</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -2002,7 +2002,7 @@
         <v>2320</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -2034,7 +2034,7 @@
         <v>2482</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -2066,7 +2066,7 @@
         <v>2004</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2098,7 +2098,7 @@
         <v>2160</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2130,7 +2130,7 @@
         <v>2320</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2162,7 +2162,7 @@
         <v>2482</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2194,7 +2194,7 @@
         <v>2006</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2226,7 +2226,7 @@
         <v>2162</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -2258,7 +2258,7 @@
         <v>2321</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2290,7 +2290,7 @@
         <v>2483</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -2318,10 +2318,10 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -2352,10 +2352,10 @@
         <v>2660</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -2386,10 +2386,10 @@
         <v>2643</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -2420,10 +2420,10 @@
         <v>2678</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -2454,10 +2454,10 @@
         <v>2659</v>
       </c>
       <c r="G46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -2488,10 +2488,10 @@
         <v>2660</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -2518,10 +2518,10 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -2548,10 +2548,10 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -2582,10 +2582,10 @@
         <v>3496</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -2616,10 +2616,10 @@
         <v>3494</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2650,10 +2650,10 @@
         <v>3493</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -2680,10 +2680,10 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -2710,10 +2710,10 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -2744,10 +2744,10 @@
         <v>2630</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -2778,10 +2778,10 @@
         <v>2665</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -2812,10 +2812,10 @@
         <v>2647</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -2842,10 +2842,10 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -2872,10 +2872,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -2906,7 +2906,7 @@
         <v>2840</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -2938,7 +2938,7 @@
         <v>3036</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -2970,7 +2970,7 @@
         <v>3250</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -3002,7 +3002,7 @@
         <v>2655</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -3034,7 +3034,7 @@
         <v>2834</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -3066,7 +3066,7 @@
         <v>3030</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -3098,7 +3098,7 @@
         <v>3243</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -3130,7 +3130,7 @@
         <v>2652</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -3162,7 +3162,7 @@
         <v>2831</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -3194,7 +3194,7 @@
         <v>3025</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -3226,7 +3226,7 @@
         <v>3238</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -3254,10 +3254,10 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -3288,10 +3288,10 @@
         <v>3570</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -3322,10 +3322,10 @@
         <v>3542</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -3356,10 +3356,10 @@
         <v>3597</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -3390,10 +3390,10 @@
         <v>3568</v>
       </c>
       <c r="G75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -3424,10 +3424,10 @@
         <v>3571</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
@@ -3454,10 +3454,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -3484,10 +3484,10 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
@@ -3514,10 +3514,10 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -3544,10 +3544,10 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -3574,10 +3574,10 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -3604,10 +3604,10 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -3634,10 +3634,10 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
@@ -3668,10 +3668,10 @@
         <v>3497</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
@@ -3702,10 +3702,10 @@
         <v>3552</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
@@ -3736,10 +3736,10 @@
         <v>3523</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
@@ -3766,10 +3766,10 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -3796,10 +3796,10 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
@@ -3830,7 +3830,7 @@
         <v>3862</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -3858,7 +3858,7 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -3886,7 +3886,7 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -3918,7 +3918,7 @@
         <v>3553</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -3950,7 +3950,7 @@
         <v>3842</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -3978,7 +3978,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -4006,7 +4006,7 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
@@ -4038,7 +4038,7 @@
         <v>3539</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
@@ -4070,7 +4070,7 @@
         <v>3827</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
@@ -4098,7 +4098,7 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
@@ -4126,7 +4126,7 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -4154,10 +4154,10 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
@@ -4184,10 +4184,10 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
@@ -4214,10 +4214,10 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
@@ -4244,10 +4244,10 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -4274,10 +4274,10 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
@@ -4304,10 +4304,10 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -4334,10 +4334,10 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -4364,10 +4364,10 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
@@ -4394,10 +4394,10 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -4424,10 +4424,10 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
@@ -4454,10 +4454,10 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -4484,10 +4484,10 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
@@ -4514,10 +4514,10 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -4544,10 +4544,10 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -4574,10 +4574,10 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -4604,10 +4604,10 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -4634,10 +4634,10 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -4664,10 +4664,10 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -4694,7 +4694,7 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -4722,7 +4722,7 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -4750,7 +4750,7 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
@@ -4778,7 +4778,7 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -4806,7 +4806,7 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
@@ -4834,7 +4834,7 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
@@ -4862,7 +4862,7 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
@@ -4890,7 +4890,7 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
@@ -4918,7 +4918,7 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
@@ -4946,7 +4946,7 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
@@ -4974,7 +4974,7 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
@@ -5002,10 +5002,10 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I129" s="1"/>
       <c r="J129" s="1"/>
@@ -5032,10 +5032,10 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I130" s="1"/>
       <c r="J130" s="1"/>
@@ -5062,10 +5062,10 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I131" s="1"/>
       <c r="J131" s="1"/>
@@ -5092,10 +5092,10 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I132" s="1"/>
       <c r="J132" s="1"/>
@@ -5122,10 +5122,10 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I133" s="1"/>
       <c r="J133" s="1"/>
@@ -5152,10 +5152,10 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I134" s="1"/>
       <c r="J134" s="1"/>
@@ -5182,10 +5182,10 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I135" s="1"/>
       <c r="J135" s="1"/>
@@ -5212,10 +5212,10 @@
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I136" s="1"/>
       <c r="J136" s="1"/>
@@ -5242,10 +5242,10 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -5272,10 +5272,10 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I138" s="1"/>
       <c r="J138" s="1"/>
@@ -5302,10 +5302,10 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I139" s="1"/>
       <c r="J139" s="1"/>
@@ -5332,10 +5332,10 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
@@ -5362,10 +5362,10 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
@@ -5392,10 +5392,10 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I142" s="1"/>
       <c r="J142" s="1"/>
@@ -5422,10 +5422,10 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I143" s="1"/>
       <c r="J143" s="1"/>
@@ -5452,10 +5452,10 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I144" s="1"/>
       <c r="J144" s="1"/>
@@ -5482,10 +5482,10 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I145" s="1"/>
       <c r="J145" s="1"/>
@@ -5512,10 +5512,10 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I146" s="1"/>
       <c r="J146" s="1"/>
@@ -5542,7 +5542,7 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H147" s="1"/>
       <c r="I147" s="1"/>
@@ -5570,7 +5570,7 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H148" s="1"/>
       <c r="I148" s="1"/>
@@ -5598,7 +5598,7 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H149" s="1"/>
       <c r="I149" s="1"/>
@@ -5626,7 +5626,7 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
@@ -5654,7 +5654,7 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H151" s="1"/>
       <c r="I151" s="1"/>
@@ -5682,7 +5682,7 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H152" s="1"/>
       <c r="I152" s="1"/>
@@ -5710,7 +5710,7 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -5738,7 +5738,7 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H154" s="1"/>
       <c r="I154" s="1"/>
@@ -5766,7 +5766,7 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -5794,7 +5794,7 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H156" s="1"/>
       <c r="I156" s="1"/>
@@ -5822,7 +5822,7 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
@@ -5850,10 +5850,10 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
@@ -5884,10 +5884,10 @@
         <v>2012</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
@@ -5918,10 +5918,10 @@
         <v>1996</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I160" s="1"/>
       <c r="J160" s="1"/>
@@ -5952,10 +5952,10 @@
         <v>2028</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1"/>
@@ -5986,10 +5986,10 @@
         <v>2011</v>
       </c>
       <c r="G162" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H162" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1"/>
@@ -6020,10 +6020,10 @@
         <v>2011</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I163" s="1"/>
       <c r="J163" s="1"/>
@@ -6050,10 +6050,10 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I164" s="1"/>
       <c r="J164" s="1"/>
@@ -6080,10 +6080,10 @@
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I165" s="1"/>
       <c r="J165" s="1"/>
@@ -6114,10 +6114,10 @@
         <v>2685</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I166" s="1"/>
       <c r="J166" s="1"/>
@@ -6148,10 +6148,10 @@
         <v>2682</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I167" s="1"/>
       <c r="J167" s="1"/>
@@ -6182,10 +6182,10 @@
         <v>2683</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I168" s="1"/>
       <c r="J168" s="1"/>
@@ -6212,10 +6212,10 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I169" s="1"/>
       <c r="J169" s="1"/>
@@ -6242,10 +6242,10 @@
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I170" s="1"/>
       <c r="J170" s="1"/>
@@ -6276,10 +6276,10 @@
         <v>1989</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I171" s="1"/>
       <c r="J171" s="1"/>
@@ -6310,10 +6310,10 @@
         <v>2025</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I172" s="1"/>
       <c r="J172" s="1"/>
@@ -6344,10 +6344,10 @@
         <v>2006</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I173" s="1"/>
       <c r="J173" s="1"/>
@@ -6374,10 +6374,10 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
@@ -6404,10 +6404,10 @@
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I175" s="1"/>
       <c r="J175" s="1"/>
@@ -6438,7 +6438,7 @@
         <v>2173</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
@@ -6470,7 +6470,7 @@
         <v>2338</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
@@ -6502,7 +6502,7 @@
         <v>2507</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
@@ -6534,7 +6534,7 @@
         <v>2010</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
@@ -6566,7 +6566,7 @@
         <v>2176</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -6598,7 +6598,7 @@
         <v>2344</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
@@ -6630,7 +6630,7 @@
         <v>2515</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
@@ -6662,7 +6662,7 @@
         <v>2008</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
@@ -6694,7 +6694,7 @@
         <v>2178</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
@@ -6726,7 +6726,7 @@
         <v>2351</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
@@ -6758,7 +6758,7 @@
         <v>2527</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
@@ -6786,10 +6786,10 @@
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I187" s="1"/>
       <c r="J187" s="1"/>
@@ -6820,10 +6820,10 @@
         <v>2684</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I188" s="1"/>
       <c r="J188" s="1"/>
@@ -6854,10 +6854,10 @@
         <v>2666</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I189" s="1"/>
       <c r="J189" s="1"/>
@@ -6888,10 +6888,10 @@
         <v>2702</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I190" s="1"/>
       <c r="J190" s="1"/>
@@ -6922,10 +6922,10 @@
         <v>2684</v>
       </c>
       <c r="G191" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H191" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H191" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I191" s="1"/>
       <c r="J191" s="1"/>
@@ -6956,10 +6956,10 @@
         <v>2683</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I192" s="1"/>
       <c r="J192" s="1"/>
@@ -6986,10 +6986,10 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I193" s="1"/>
       <c r="J193" s="1"/>
@@ -7016,10 +7016,10 @@
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I194" s="1"/>
       <c r="J194" s="1"/>
@@ -7050,10 +7050,10 @@
         <v>3544</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I195" s="1"/>
       <c r="J195" s="1"/>
@@ -7084,10 +7084,10 @@
         <v>3539</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I196" s="1"/>
       <c r="J196" s="1"/>
@@ -7118,10 +7118,10 @@
         <v>3541</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I197" s="1"/>
       <c r="J197" s="1"/>
@@ -7148,10 +7148,10 @@
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I198" s="1"/>
       <c r="J198" s="1"/>
@@ -7178,10 +7178,10 @@
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I199" s="1"/>
       <c r="J199" s="1"/>
@@ -7212,10 +7212,10 @@
         <v>2693</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I200" s="1"/>
       <c r="J200" s="1"/>
@@ -7246,10 +7246,10 @@
         <v>2732</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I201" s="1"/>
       <c r="J201" s="1"/>
@@ -7280,10 +7280,10 @@
         <v>2712</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I202" s="1"/>
       <c r="J202" s="1"/>
@@ -7310,10 +7310,10 @@
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I203" s="1"/>
       <c r="J203" s="1"/>
@@ -7340,10 +7340,10 @@
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I204" s="1"/>
       <c r="J204" s="1"/>
@@ -7374,7 +7374,7 @@
         <v>2870</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H205" s="1"/>
       <c r="I205" s="1"/>
@@ -7406,7 +7406,7 @@
         <v>3073</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
@@ -7438,7 +7438,7 @@
         <v>3292</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
@@ -7470,7 +7470,7 @@
         <v>2693</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
@@ -7502,7 +7502,7 @@
         <v>2882</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
@@ -7534,7 +7534,7 @@
         <v>3090</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
@@ -7566,7 +7566,7 @@
         <v>3316</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
@@ -7598,7 +7598,7 @@
         <v>2703</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
@@ -7630,7 +7630,7 @@
         <v>2898</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
@@ -7662,7 +7662,7 @@
         <v>3109</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
@@ -7694,7 +7694,7 @@
         <v>3342</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
@@ -7722,10 +7722,10 @@
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I216" s="1"/>
       <c r="J216" s="1"/>
@@ -7756,10 +7756,10 @@
         <v>3519</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I217" s="1"/>
       <c r="J217" s="1"/>
@@ -7790,10 +7790,10 @@
         <v>3494</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I218" s="1"/>
       <c r="J218" s="1"/>
@@ -7824,10 +7824,10 @@
         <v>3546</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I219" s="1"/>
       <c r="J219" s="1"/>
@@ -7858,10 +7858,10 @@
         <v>3521</v>
       </c>
       <c r="G220" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H220" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H220" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I220" s="1"/>
       <c r="J220" s="1"/>
@@ -7892,10 +7892,10 @@
         <v>3517</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I221" s="1"/>
       <c r="J221" s="1"/>
@@ -7922,10 +7922,10 @@
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I222" s="1"/>
       <c r="J222" s="1"/>
@@ -7952,10 +7952,10 @@
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I223" s="1"/>
       <c r="J223" s="1"/>
@@ -7982,10 +7982,10 @@
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I224" s="1"/>
       <c r="J224" s="1"/>
@@ -8012,10 +8012,10 @@
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I225" s="1"/>
       <c r="J225" s="1"/>
@@ -8042,10 +8042,10 @@
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I226" s="1"/>
       <c r="J226" s="1"/>
@@ -8072,10 +8072,10 @@
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I227" s="1"/>
       <c r="J227" s="1"/>
@@ -8102,10 +8102,10 @@
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I228" s="1"/>
       <c r="J228" s="1"/>
@@ -8132,10 +8132,10 @@
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I229" s="1"/>
       <c r="J229" s="1"/>
@@ -8162,10 +8162,10 @@
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I230" s="1"/>
       <c r="J230" s="1"/>
@@ -8192,10 +8192,10 @@
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I231" s="1"/>
       <c r="J231" s="1"/>
@@ -8222,10 +8222,10 @@
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I232" s="1"/>
       <c r="J232" s="1"/>
@@ -8252,10 +8252,10 @@
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I233" s="1"/>
       <c r="J233" s="1"/>
@@ -8286,7 +8286,7 @@
         <v>3797</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
@@ -8314,7 +8314,7 @@
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
@@ -8342,7 +8342,7 @@
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
@@ -8374,7 +8374,7 @@
         <v>3529</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
@@ -8406,7 +8406,7 @@
         <v>3813</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
@@ -8434,7 +8434,7 @@
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
@@ -8462,7 +8462,7 @@
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
@@ -8494,7 +8494,7 @@
         <v>3543</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
@@ -8526,7 +8526,7 @@
         <v>3837</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
@@ -8554,7 +8554,7 @@
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
@@ -8582,7 +8582,7 @@
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
@@ -8610,10 +8610,10 @@
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I245" s="1"/>
       <c r="J245" s="1"/>
@@ -8640,10 +8640,10 @@
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I246" s="1"/>
       <c r="J246" s="1"/>
@@ -8670,10 +8670,10 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I247" s="1"/>
       <c r="J247" s="1"/>
@@ -8700,10 +8700,10 @@
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I248" s="1"/>
       <c r="J248" s="1"/>
@@ -8730,10 +8730,10 @@
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H249" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H249" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I249" s="1"/>
       <c r="J249" s="1"/>
@@ -8760,10 +8760,10 @@
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I250" s="1"/>
       <c r="J250" s="1"/>
@@ -8790,10 +8790,10 @@
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I251" s="1"/>
       <c r="J251" s="1"/>
@@ -8820,10 +8820,10 @@
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I252" s="1"/>
       <c r="J252" s="1"/>
@@ -8850,10 +8850,10 @@
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I253" s="1"/>
       <c r="J253" s="1"/>
@@ -8880,10 +8880,10 @@
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I254" s="1"/>
       <c r="J254" s="1"/>
@@ -8910,10 +8910,10 @@
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I255" s="1"/>
       <c r="J255" s="1"/>
@@ -8940,10 +8940,10 @@
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I256" s="1"/>
       <c r="J256" s="1"/>
@@ -8970,10 +8970,10 @@
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I257" s="1"/>
       <c r="J257" s="1"/>
@@ -9000,10 +9000,10 @@
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I258" s="1"/>
       <c r="J258" s="1"/>
@@ -9030,10 +9030,10 @@
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I259" s="1"/>
       <c r="J259" s="1"/>
@@ -9060,10 +9060,10 @@
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I260" s="1"/>
       <c r="J260" s="1"/>
@@ -9090,10 +9090,10 @@
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
@@ -9120,10 +9120,10 @@
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
@@ -9150,7 +9150,7 @@
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
@@ -9178,7 +9178,7 @@
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
@@ -9206,7 +9206,7 @@
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
@@ -9234,7 +9234,7 @@
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
@@ -9262,7 +9262,7 @@
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
@@ -9290,7 +9290,7 @@
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
@@ -9318,7 +9318,7 @@
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
@@ -9346,7 +9346,7 @@
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
@@ -9374,7 +9374,7 @@
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
@@ -9402,7 +9402,7 @@
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
@@ -9430,7 +9430,7 @@
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
       <c r="G273" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H273" s="1"/>
       <c r="I273" s="1"/>
@@ -9458,10 +9458,10 @@
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="G274" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I274" s="1"/>
       <c r="J274" s="1"/>
@@ -9488,10 +9488,10 @@
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I275" s="1"/>
       <c r="J275" s="1"/>
@@ -9518,10 +9518,10 @@
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I276" s="1"/>
       <c r="J276" s="1"/>
@@ -9548,10 +9548,10 @@
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
       <c r="G277" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I277" s="1"/>
       <c r="J277" s="1"/>
@@ -9578,10 +9578,10 @@
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H278" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H278" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I278" s="1"/>
       <c r="J278" s="1"/>
@@ -9608,10 +9608,10 @@
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I279" s="1"/>
       <c r="J279" s="1"/>
@@ -9638,10 +9638,10 @@
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I280" s="1"/>
       <c r="J280" s="1"/>
@@ -9668,10 +9668,10 @@
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I281" s="1"/>
       <c r="J281" s="1"/>
@@ -9698,10 +9698,10 @@
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I282" s="1"/>
       <c r="J282" s="1"/>
@@ -9728,10 +9728,10 @@
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I283" s="1"/>
       <c r="J283" s="1"/>
@@ -9758,10 +9758,10 @@
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
       <c r="G284" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I284" s="1"/>
       <c r="J284" s="1"/>
@@ -9788,10 +9788,10 @@
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I285" s="1"/>
       <c r="J285" s="1"/>
@@ -9818,10 +9818,10 @@
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I286" s="1"/>
       <c r="J286" s="1"/>
@@ -9848,10 +9848,10 @@
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
       <c r="G287" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I287" s="1"/>
       <c r="J287" s="1"/>
@@ -9878,10 +9878,10 @@
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
       <c r="G288" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I288" s="1"/>
       <c r="J288" s="1"/>
@@ -9908,10 +9908,10 @@
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
       <c r="G289" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I289" s="1"/>
       <c r="J289" s="1"/>
@@ -9938,10 +9938,10 @@
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I290" s="1"/>
       <c r="J290" s="1"/>
@@ -9968,10 +9968,10 @@
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I291" s="1"/>
       <c r="J291" s="1"/>
@@ -9998,7 +9998,7 @@
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
       <c r="G292" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H292" s="1"/>
       <c r="I292" s="1"/>
@@ -10026,7 +10026,7 @@
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H293" s="1"/>
       <c r="I293" s="1"/>
@@ -10054,7 +10054,7 @@
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H294" s="1"/>
       <c r="I294" s="1"/>
@@ -10082,7 +10082,7 @@
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
       <c r="G295" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H295" s="1"/>
       <c r="I295" s="1"/>
@@ -10110,7 +10110,7 @@
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
       <c r="G296" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H296" s="1"/>
       <c r="I296" s="1"/>
@@ -10138,7 +10138,7 @@
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H297" s="1"/>
       <c r="I297" s="1"/>
@@ -10166,7 +10166,7 @@
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
       <c r="G298" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H298" s="1"/>
       <c r="I298" s="1"/>
@@ -10194,7 +10194,7 @@
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
       <c r="G299" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H299" s="1"/>
       <c r="I299" s="1"/>
@@ -10222,7 +10222,7 @@
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
       <c r="G300" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H300" s="1"/>
       <c r="I300" s="1"/>
@@ -10250,7 +10250,7 @@
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
       <c r="G301" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H301" s="1"/>
       <c r="I301" s="1"/>
@@ -10278,7 +10278,7 @@
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H302" s="1"/>
       <c r="I302" s="1"/>
@@ -10306,10 +10306,10 @@
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="G303" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H303" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I303" s="1"/>
       <c r="J303" s="1"/>
@@ -10340,10 +10340,10 @@
         <v>2000</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I304" s="1"/>
       <c r="J304" s="1"/>
@@ -10374,10 +10374,10 @@
         <v>1983</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I305" s="1"/>
       <c r="J305" s="1"/>
@@ -10408,10 +10408,10 @@
         <v>2018</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I306" s="1"/>
       <c r="J306" s="1"/>
@@ -10442,10 +10442,10 @@
         <v>1999</v>
       </c>
       <c r="G307" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H307" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H307" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I307" s="1"/>
       <c r="J307" s="1"/>
@@ -10476,10 +10476,10 @@
         <v>2000</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I308" s="1"/>
       <c r="J308" s="1"/>
@@ -10506,10 +10506,10 @@
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I309" s="1"/>
       <c r="J309" s="1"/>
@@ -10536,10 +10536,10 @@
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I310" s="1"/>
       <c r="J310" s="1"/>
@@ -10570,10 +10570,10 @@
         <v>2747</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I311" s="1"/>
       <c r="J311" s="1"/>
@@ -10604,10 +10604,10 @@
         <v>2741</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I312" s="1"/>
       <c r="J312" s="1"/>
@@ -10638,10 +10638,10 @@
         <v>2743</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I313" s="1"/>
       <c r="J313" s="1"/>
@@ -10668,10 +10668,10 @@
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I314" s="1"/>
       <c r="J314" s="1"/>
@@ -10698,10 +10698,10 @@
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I315" s="1"/>
       <c r="J315" s="1"/>
@@ -10728,10 +10728,10 @@
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I316" s="1"/>
       <c r="J316" s="1"/>
@@ -10758,10 +10758,10 @@
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I317" s="1"/>
       <c r="J317" s="1"/>
@@ -10788,10 +10788,10 @@
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
       <c r="G318" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I318" s="1"/>
       <c r="J318" s="1"/>
@@ -10818,10 +10818,10 @@
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I319" s="1"/>
       <c r="J319" s="1"/>
@@ -10848,10 +10848,10 @@
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I320" s="1"/>
       <c r="J320" s="1"/>
@@ -10882,7 +10882,7 @@
         <v>2179</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H321" s="1"/>
       <c r="I321" s="1"/>
@@ -10914,7 +10914,7 @@
         <v>2362</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H322" s="1"/>
       <c r="I322" s="1"/>
@@ -10946,7 +10946,7 @@
         <v>2548</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H323" s="1"/>
       <c r="I323" s="1"/>
@@ -10974,7 +10974,7 @@
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
       <c r="G324" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H324" s="1"/>
       <c r="I324" s="1"/>
@@ -11002,7 +11002,7 @@
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
       <c r="G325" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H325" s="1"/>
       <c r="I325" s="1"/>
@@ -11030,7 +11030,7 @@
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
       <c r="G326" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H326" s="1"/>
       <c r="I326" s="1"/>
@@ -11058,7 +11058,7 @@
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
       <c r="G327" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H327" s="1"/>
       <c r="I327" s="1"/>
@@ -11086,7 +11086,7 @@
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H328" s="1"/>
       <c r="I328" s="1"/>
@@ -11114,7 +11114,7 @@
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
       <c r="G329" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H329" s="1"/>
       <c r="I329" s="1"/>
@@ -11142,7 +11142,7 @@
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
       <c r="G330" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H330" s="1"/>
       <c r="I330" s="1"/>
@@ -11170,7 +11170,7 @@
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
       <c r="G331" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H331" s="1"/>
       <c r="I331" s="1"/>
@@ -11198,10 +11198,10 @@
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="G332" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H332" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I332" s="1"/>
       <c r="J332" s="1"/>
@@ -11228,10 +11228,10 @@
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I333" s="1"/>
       <c r="J333" s="1"/>
@@ -11258,10 +11258,10 @@
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
@@ -11288,10 +11288,10 @@
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I335" s="1"/>
       <c r="J335" s="1"/>
@@ -11318,10 +11318,10 @@
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H336" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H336" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
@@ -11348,10 +11348,10 @@
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
       <c r="G337" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
@@ -11378,10 +11378,10 @@
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
@@ -11408,10 +11408,10 @@
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
@@ -11438,10 +11438,10 @@
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I340" s="1"/>
       <c r="J340" s="1"/>
@@ -11468,10 +11468,10 @@
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
@@ -11498,10 +11498,10 @@
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
       <c r="G342" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I342" s="1"/>
       <c r="J342" s="1"/>
@@ -11528,10 +11528,10 @@
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
@@ -11558,10 +11558,10 @@
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
@@ -11588,10 +11588,10 @@
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
       <c r="G345" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
@@ -11618,10 +11618,10 @@
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
       <c r="G346" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
@@ -11648,10 +11648,10 @@
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I347" s="1"/>
       <c r="J347" s="1"/>
@@ -11678,10 +11678,10 @@
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
@@ -11708,10 +11708,10 @@
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I349" s="1"/>
       <c r="J349" s="1"/>
@@ -11738,7 +11738,7 @@
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
       <c r="G350" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H350" s="1"/>
       <c r="I350" s="1"/>
@@ -11766,7 +11766,7 @@
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
       <c r="G351" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H351" s="1"/>
       <c r="I351" s="1"/>
@@ -11794,7 +11794,7 @@
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
       <c r="G352" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H352" s="1"/>
       <c r="I352" s="1"/>
@@ -11822,7 +11822,7 @@
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
       <c r="G353" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H353" s="1"/>
       <c r="I353" s="1"/>
@@ -11850,7 +11850,7 @@
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
       <c r="G354" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H354" s="1"/>
       <c r="I354" s="1"/>
@@ -11878,7 +11878,7 @@
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
       <c r="G355" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H355" s="1"/>
       <c r="I355" s="1"/>
@@ -11906,7 +11906,7 @@
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
       <c r="G356" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H356" s="1"/>
       <c r="I356" s="1"/>
@@ -11934,7 +11934,7 @@
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H357" s="1"/>
       <c r="I357" s="1"/>
@@ -11962,7 +11962,7 @@
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H358" s="1"/>
       <c r="I358" s="1"/>
@@ -11990,7 +11990,7 @@
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H359" s="1"/>
       <c r="I359" s="1"/>
@@ -12018,7 +12018,7 @@
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
       <c r="G360" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H360" s="1"/>
       <c r="I360" s="1"/>
@@ -12046,10 +12046,10 @@
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
       <c r="G361" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H361" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
@@ -12076,10 +12076,10 @@
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
       <c r="G362" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
@@ -12106,10 +12106,10 @@
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
       <c r="G363" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
@@ -12136,10 +12136,10 @@
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
       <c r="G364" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
@@ -12166,10 +12166,10 @@
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H365" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H365" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
@@ -12196,10 +12196,10 @@
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H366" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
@@ -12226,10 +12226,10 @@
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
       <c r="G367" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
@@ -12256,10 +12256,10 @@
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
       <c r="G368" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
@@ -12286,10 +12286,10 @@
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H369" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
@@ -12316,10 +12316,10 @@
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
       <c r="G370" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H370" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
@@ -12346,10 +12346,10 @@
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
       <c r="G371" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
@@ -12376,10 +12376,10 @@
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
       <c r="G372" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
@@ -12406,10 +12406,10 @@
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
       <c r="G373" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
@@ -12436,10 +12436,10 @@
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
@@ -12466,10 +12466,10 @@
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
       <c r="G375" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
@@ -12496,10 +12496,10 @@
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
       <c r="G376" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
@@ -12526,10 +12526,10 @@
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
       <c r="G377" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H377" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
@@ -12556,10 +12556,10 @@
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
       <c r="G378" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H378" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I378" s="1"/>
       <c r="J378" s="1"/>
@@ -12586,7 +12586,7 @@
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H379" s="1"/>
       <c r="I379" s="1"/>
@@ -12614,7 +12614,7 @@
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
       <c r="G380" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H380" s="1"/>
       <c r="I380" s="1"/>
@@ -12642,7 +12642,7 @@
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
       <c r="G381" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H381" s="1"/>
       <c r="I381" s="1"/>
@@ -12670,7 +12670,7 @@
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
       <c r="G382" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H382" s="1"/>
       <c r="I382" s="1"/>
@@ -12698,7 +12698,7 @@
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
       <c r="G383" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H383" s="1"/>
       <c r="I383" s="1"/>
@@ -12726,7 +12726,7 @@
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
       <c r="G384" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H384" s="1"/>
       <c r="I384" s="1"/>
@@ -12754,7 +12754,7 @@
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
       <c r="G385" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H385" s="1"/>
       <c r="I385" s="1"/>
@@ -12782,7 +12782,7 @@
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
       <c r="G386" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H386" s="1"/>
       <c r="I386" s="1"/>
@@ -12810,7 +12810,7 @@
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
       <c r="G387" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H387" s="1"/>
       <c r="I387" s="1"/>
@@ -12838,7 +12838,7 @@
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
       <c r="G388" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H388" s="1"/>
       <c r="I388" s="1"/>
@@ -12866,7 +12866,7 @@
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
       <c r="G389" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H389" s="1"/>
       <c r="I389" s="1"/>
@@ -12894,10 +12894,10 @@
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
       <c r="G390" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H390" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I390" s="1"/>
       <c r="J390" s="1"/>
@@ -12924,10 +12924,10 @@
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
       <c r="G391" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I391" s="1"/>
       <c r="J391" s="1"/>
@@ -12954,10 +12954,10 @@
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I392" s="1"/>
       <c r="J392" s="1"/>
@@ -12984,10 +12984,10 @@
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
       <c r="G393" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I393" s="1"/>
       <c r="J393" s="1"/>
@@ -13014,10 +13014,10 @@
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H394" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H394" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I394" s="1"/>
       <c r="J394" s="1"/>
@@ -13044,10 +13044,10 @@
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I395" s="1"/>
       <c r="J395" s="1"/>
@@ -13074,10 +13074,10 @@
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I396" s="1"/>
       <c r="J396" s="1"/>
@@ -13104,10 +13104,10 @@
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
       <c r="G397" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H397" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I397" s="1"/>
       <c r="J397" s="1"/>
@@ -13134,10 +13134,10 @@
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
       <c r="G398" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I398" s="1"/>
       <c r="J398" s="1"/>
@@ -13164,10 +13164,10 @@
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
       <c r="G399" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I399" s="1"/>
       <c r="J399" s="1"/>
@@ -13194,10 +13194,10 @@
       <c r="E400" s="2"/>
       <c r="F400" s="2"/>
       <c r="G400" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I400" s="1"/>
       <c r="J400" s="1"/>
@@ -13224,10 +13224,10 @@
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
       <c r="G401" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I401" s="1"/>
       <c r="J401" s="1"/>
@@ -13254,10 +13254,10 @@
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
       <c r="G402" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H402" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I402" s="1"/>
       <c r="J402" s="1"/>
@@ -13284,10 +13284,10 @@
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
       <c r="G403" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I403" s="1"/>
       <c r="J403" s="1"/>
@@ -13314,10 +13314,10 @@
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
       <c r="G404" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I404" s="1"/>
       <c r="J404" s="1"/>
@@ -13344,10 +13344,10 @@
       <c r="E405" s="2"/>
       <c r="F405" s="2"/>
       <c r="G405" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I405" s="1"/>
       <c r="J405" s="1"/>
@@ -13374,10 +13374,10 @@
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
       <c r="G406" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I406" s="1"/>
       <c r="J406" s="1"/>
@@ -13404,10 +13404,10 @@
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
       <c r="G407" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H407" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I407" s="1"/>
       <c r="J407" s="1"/>
@@ -13434,7 +13434,7 @@
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
       <c r="G408" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H408" s="1"/>
       <c r="I408" s="1"/>
@@ -13462,7 +13462,7 @@
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
       <c r="G409" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H409" s="1"/>
       <c r="I409" s="1"/>
@@ -13490,7 +13490,7 @@
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
       <c r="G410" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H410" s="1"/>
       <c r="I410" s="1"/>
@@ -13518,7 +13518,7 @@
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
       <c r="G411" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H411" s="1"/>
       <c r="I411" s="1"/>
@@ -13546,7 +13546,7 @@
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H412" s="1"/>
       <c r="I412" s="1"/>
@@ -13574,7 +13574,7 @@
       <c r="E413" s="2"/>
       <c r="F413" s="2"/>
       <c r="G413" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H413" s="1"/>
       <c r="I413" s="1"/>
@@ -13602,7 +13602,7 @@
       <c r="E414" s="2"/>
       <c r="F414" s="2"/>
       <c r="G414" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H414" s="1"/>
       <c r="I414" s="1"/>
@@ -13630,7 +13630,7 @@
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H415" s="1"/>
       <c r="I415" s="1"/>
@@ -13658,7 +13658,7 @@
       <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H416" s="1"/>
       <c r="I416" s="1"/>
@@ -13686,7 +13686,7 @@
       <c r="E417" s="2"/>
       <c r="F417" s="2"/>
       <c r="G417" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H417" s="1"/>
       <c r="I417" s="1"/>
@@ -13714,7 +13714,7 @@
       <c r="E418" s="2"/>
       <c r="F418" s="2"/>
       <c r="G418" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H418" s="1"/>
       <c r="I418" s="1"/>
@@ -13742,10 +13742,10 @@
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
       <c r="G419" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H419" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I419" s="1"/>
       <c r="J419" s="1"/>
@@ -13772,10 +13772,10 @@
       <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H420" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I420" s="1"/>
       <c r="J420" s="1"/>
@@ -13802,10 +13802,10 @@
       <c r="E421" s="2"/>
       <c r="F421" s="2"/>
       <c r="G421" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I421" s="1"/>
       <c r="J421" s="1"/>
@@ -13832,10 +13832,10 @@
       <c r="E422" s="2"/>
       <c r="F422" s="2"/>
       <c r="G422" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I422" s="1"/>
       <c r="J422" s="1"/>
@@ -13862,10 +13862,10 @@
       <c r="E423" s="2"/>
       <c r="F423" s="2"/>
       <c r="G423" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H423" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H423" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I423" s="1"/>
       <c r="J423" s="1"/>
@@ -13892,10 +13892,10 @@
       <c r="E424" s="2"/>
       <c r="F424" s="2"/>
       <c r="G424" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I424" s="1"/>
       <c r="J424" s="1"/>
@@ -13922,10 +13922,10 @@
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
       <c r="G425" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I425" s="1"/>
       <c r="J425" s="1"/>
@@ -13952,10 +13952,10 @@
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
       <c r="G426" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H426" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I426" s="1"/>
       <c r="J426" s="1"/>
@@ -13982,10 +13982,10 @@
       <c r="E427" s="2"/>
       <c r="F427" s="2"/>
       <c r="G427" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I427" s="1"/>
       <c r="J427" s="1"/>
@@ -14012,10 +14012,10 @@
       <c r="E428" s="2"/>
       <c r="F428" s="2"/>
       <c r="G428" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I428" s="1"/>
       <c r="J428" s="1"/>
@@ -14042,10 +14042,10 @@
       <c r="E429" s="2"/>
       <c r="F429" s="2"/>
       <c r="G429" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I429" s="1"/>
       <c r="J429" s="1"/>
@@ -14072,10 +14072,10 @@
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
       <c r="G430" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I430" s="1"/>
       <c r="J430" s="1"/>
@@ -14102,10 +14102,10 @@
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
       <c r="G431" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I431" s="1"/>
       <c r="J431" s="1"/>
@@ -14132,10 +14132,10 @@
       <c r="E432" s="2"/>
       <c r="F432" s="2"/>
       <c r="G432" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I432" s="1"/>
       <c r="J432" s="1"/>
@@ -14162,10 +14162,10 @@
       <c r="E433" s="2"/>
       <c r="F433" s="2"/>
       <c r="G433" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I433" s="1"/>
       <c r="J433" s="1"/>
@@ -14192,10 +14192,10 @@
       <c r="E434" s="2"/>
       <c r="F434" s="2"/>
       <c r="G434" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I434" s="1"/>
       <c r="J434" s="1"/>
@@ -14222,10 +14222,10 @@
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I435" s="1"/>
       <c r="J435" s="1"/>
@@ -14252,10 +14252,10 @@
       <c r="E436" s="1"/>
       <c r="F436" s="1"/>
       <c r="G436" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I436" s="1"/>
       <c r="J436" s="1"/>
@@ -14282,7 +14282,7 @@
       <c r="E437" s="2"/>
       <c r="F437" s="2"/>
       <c r="G437" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H437" s="1"/>
       <c r="I437" s="1"/>
@@ -14310,7 +14310,7 @@
       <c r="E438" s="2"/>
       <c r="F438" s="2"/>
       <c r="G438" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H438" s="1"/>
       <c r="I438" s="1"/>
@@ -14338,7 +14338,7 @@
       <c r="E439" s="2"/>
       <c r="F439" s="2"/>
       <c r="G439" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H439" s="1"/>
       <c r="I439" s="1"/>
@@ -14366,7 +14366,7 @@
       <c r="E440" s="2"/>
       <c r="F440" s="2"/>
       <c r="G440" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H440" s="1"/>
       <c r="I440" s="1"/>
@@ -14394,7 +14394,7 @@
       <c r="E441" s="2"/>
       <c r="F441" s="2"/>
       <c r="G441" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H441" s="1"/>
       <c r="I441" s="1"/>
@@ -14422,7 +14422,7 @@
       <c r="E442" s="2"/>
       <c r="F442" s="2"/>
       <c r="G442" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H442" s="1"/>
       <c r="I442" s="1"/>
@@ -14450,7 +14450,7 @@
       <c r="E443" s="2"/>
       <c r="F443" s="2"/>
       <c r="G443" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H443" s="1"/>
       <c r="I443" s="1"/>
@@ -14478,7 +14478,7 @@
       <c r="E444" s="2"/>
       <c r="F444" s="2"/>
       <c r="G444" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H444" s="1"/>
       <c r="I444" s="1"/>
@@ -14506,7 +14506,7 @@
       <c r="E445" s="2"/>
       <c r="F445" s="2"/>
       <c r="G445" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H445" s="1"/>
       <c r="I445" s="1"/>
@@ -14534,7 +14534,7 @@
       <c r="E446" s="2"/>
       <c r="F446" s="2"/>
       <c r="G446" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H446" s="1"/>
       <c r="I446" s="1"/>
@@ -14562,7 +14562,7 @@
       <c r="E447" s="2"/>
       <c r="F447" s="2"/>
       <c r="G447" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H447" s="1"/>
       <c r="I447" s="1"/>
@@ -14590,10 +14590,10 @@
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
       <c r="G448" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H448" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I448" s="1"/>
       <c r="J448" s="1"/>
@@ -14620,10 +14620,10 @@
       <c r="E449" s="2"/>
       <c r="F449" s="2"/>
       <c r="G449" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I449" s="1"/>
       <c r="J449" s="1"/>
@@ -14650,10 +14650,10 @@
       <c r="E450" s="2"/>
       <c r="F450" s="2"/>
       <c r="G450" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I450" s="1"/>
       <c r="J450" s="1"/>
@@ -14680,10 +14680,10 @@
       <c r="E451" s="2"/>
       <c r="F451" s="2"/>
       <c r="G451" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I451" s="1"/>
       <c r="J451" s="1"/>
@@ -14710,10 +14710,10 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H452" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H452" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I452" s="1"/>
       <c r="J452" s="1"/>
@@ -14740,10 +14740,10 @@
       <c r="E453" s="2"/>
       <c r="F453" s="2"/>
       <c r="G453" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I453" s="1"/>
       <c r="J453" s="1"/>
@@ -14770,10 +14770,10 @@
       <c r="E454" s="1"/>
       <c r="F454" s="1"/>
       <c r="G454" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I454" s="1"/>
       <c r="J454" s="1"/>
@@ -14800,10 +14800,10 @@
       <c r="E455" s="1"/>
       <c r="F455" s="1"/>
       <c r="G455" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H455" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I455" s="1"/>
       <c r="J455" s="1"/>
@@ -14830,10 +14830,10 @@
       <c r="E456" s="2"/>
       <c r="F456" s="2"/>
       <c r="G456" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I456" s="1"/>
       <c r="J456" s="1"/>
@@ -14860,10 +14860,10 @@
       <c r="E457" s="2"/>
       <c r="F457" s="2"/>
       <c r="G457" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I457" s="1"/>
       <c r="J457" s="1"/>
@@ -14890,10 +14890,10 @@
       <c r="E458" s="2"/>
       <c r="F458" s="2"/>
       <c r="G458" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I458" s="1"/>
       <c r="J458" s="1"/>
@@ -14920,10 +14920,10 @@
       <c r="E459" s="1"/>
       <c r="F459" s="1"/>
       <c r="G459" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I459" s="1"/>
       <c r="J459" s="1"/>
@@ -14950,10 +14950,10 @@
       <c r="E460" s="1"/>
       <c r="F460" s="1"/>
       <c r="G460" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I460" s="1"/>
       <c r="J460" s="1"/>
@@ -14980,10 +14980,10 @@
       <c r="E461" s="2"/>
       <c r="F461" s="2"/>
       <c r="G461" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I461" s="1"/>
       <c r="J461" s="1"/>
@@ -15010,10 +15010,10 @@
       <c r="E462" s="2"/>
       <c r="F462" s="2"/>
       <c r="G462" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I462" s="1"/>
       <c r="J462" s="1"/>
@@ -15040,10 +15040,10 @@
       <c r="E463" s="2"/>
       <c r="F463" s="2"/>
       <c r="G463" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I463" s="1"/>
       <c r="J463" s="1"/>
@@ -15070,10 +15070,10 @@
       <c r="E464" s="1"/>
       <c r="F464" s="1"/>
       <c r="G464" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I464" s="1"/>
       <c r="J464" s="1"/>
@@ -15100,10 +15100,10 @@
       <c r="E465" s="1"/>
       <c r="F465" s="1"/>
       <c r="G465" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I465" s="1"/>
       <c r="J465" s="1"/>
@@ -15130,7 +15130,7 @@
       <c r="E466" s="2"/>
       <c r="F466" s="2"/>
       <c r="G466" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H466" s="1"/>
       <c r="I466" s="1"/>
@@ -15158,7 +15158,7 @@
       <c r="E467" s="2"/>
       <c r="F467" s="2"/>
       <c r="G467" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H467" s="1"/>
       <c r="I467" s="1"/>
@@ -15186,7 +15186,7 @@
       <c r="E468" s="2"/>
       <c r="F468" s="2"/>
       <c r="G468" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H468" s="1"/>
       <c r="I468" s="1"/>
@@ -15214,7 +15214,7 @@
       <c r="E469" s="2"/>
       <c r="F469" s="2"/>
       <c r="G469" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H469" s="1"/>
       <c r="I469" s="1"/>
@@ -15242,7 +15242,7 @@
       <c r="E470" s="2"/>
       <c r="F470" s="2"/>
       <c r="G470" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H470" s="1"/>
       <c r="I470" s="1"/>
@@ -15270,7 +15270,7 @@
       <c r="E471" s="2"/>
       <c r="F471" s="2"/>
       <c r="G471" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H471" s="1"/>
       <c r="I471" s="1"/>
@@ -15298,7 +15298,7 @@
       <c r="E472" s="2"/>
       <c r="F472" s="2"/>
       <c r="G472" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H472" s="1"/>
       <c r="I472" s="1"/>
@@ -15326,7 +15326,7 @@
       <c r="E473" s="2"/>
       <c r="F473" s="2"/>
       <c r="G473" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H473" s="1"/>
       <c r="I473" s="1"/>
@@ -15354,7 +15354,7 @@
       <c r="E474" s="2"/>
       <c r="F474" s="2"/>
       <c r="G474" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H474" s="1"/>
       <c r="I474" s="1"/>
@@ -15382,7 +15382,7 @@
       <c r="E475" s="2"/>
       <c r="F475" s="2"/>
       <c r="G475" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H475" s="1"/>
       <c r="I475" s="1"/>
@@ -15410,7 +15410,7 @@
       <c r="E476" s="2"/>
       <c r="F476" s="2"/>
       <c r="G476" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H476" s="1"/>
       <c r="I476" s="1"/>
@@ -15438,10 +15438,10 @@
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
       <c r="G477" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H477" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I477" s="1"/>
       <c r="J477" s="1"/>
@@ -15468,10 +15468,10 @@
       <c r="E478" s="2"/>
       <c r="F478" s="2"/>
       <c r="G478" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I478" s="1"/>
       <c r="J478" s="1"/>
@@ -15498,10 +15498,10 @@
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I479" s="1"/>
       <c r="J479" s="1"/>
@@ -15528,10 +15528,10 @@
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I480" s="1"/>
       <c r="J480" s="1"/>
@@ -15558,10 +15558,10 @@
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H481" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H481" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I481" s="1"/>
       <c r="J481" s="1"/>
@@ -15588,10 +15588,10 @@
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I482" s="1"/>
       <c r="J482" s="1"/>
@@ -15618,10 +15618,10 @@
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
       <c r="G483" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I483" s="1"/>
       <c r="J483" s="1"/>
@@ -15648,10 +15648,10 @@
       <c r="E484" s="1"/>
       <c r="F484" s="1"/>
       <c r="G484" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I484" s="1"/>
       <c r="J484" s="1"/>
@@ -15678,10 +15678,10 @@
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I485" s="1"/>
       <c r="J485" s="1"/>
@@ -15708,10 +15708,10 @@
       <c r="E486" s="2"/>
       <c r="F486" s="2"/>
       <c r="G486" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H486" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I486" s="1"/>
       <c r="J486" s="1"/>
@@ -15738,10 +15738,10 @@
       <c r="E487" s="2"/>
       <c r="F487" s="2"/>
       <c r="G487" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I487" s="1"/>
       <c r="J487" s="1"/>
@@ -15768,10 +15768,10 @@
       <c r="E488" s="1"/>
       <c r="F488" s="1"/>
       <c r="G488" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I488" s="1"/>
       <c r="J488" s="1"/>
@@ -15798,10 +15798,10 @@
       <c r="E489" s="1"/>
       <c r="F489" s="1"/>
       <c r="G489" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I489" s="1"/>
       <c r="J489" s="1"/>
@@ -15828,10 +15828,10 @@
       <c r="E490" s="2"/>
       <c r="F490" s="2"/>
       <c r="G490" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I490" s="1"/>
       <c r="J490" s="1"/>
@@ -15858,10 +15858,10 @@
       <c r="E491" s="2"/>
       <c r="F491" s="2"/>
       <c r="G491" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I491" s="1"/>
       <c r="J491" s="1"/>
@@ -15888,10 +15888,10 @@
       <c r="E492" s="2"/>
       <c r="F492" s="2"/>
       <c r="G492" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I492" s="1"/>
       <c r="J492" s="1"/>
@@ -15918,10 +15918,10 @@
       <c r="E493" s="1"/>
       <c r="F493" s="1"/>
       <c r="G493" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I493" s="1"/>
       <c r="J493" s="1"/>
@@ -15948,10 +15948,10 @@
       <c r="E494" s="1"/>
       <c r="F494" s="1"/>
       <c r="G494" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I494" s="1"/>
       <c r="J494" s="1"/>
@@ -15978,7 +15978,7 @@
       <c r="E495" s="2"/>
       <c r="F495" s="2"/>
       <c r="G495" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H495" s="1"/>
       <c r="I495" s="1"/>
@@ -16006,7 +16006,7 @@
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H496" s="1"/>
       <c r="I496" s="1"/>
@@ -16034,7 +16034,7 @@
       <c r="E497" s="2"/>
       <c r="F497" s="2"/>
       <c r="G497" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H497" s="1"/>
       <c r="I497" s="1"/>
@@ -16062,7 +16062,7 @@
       <c r="E498" s="2"/>
       <c r="F498" s="2"/>
       <c r="G498" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H498" s="1"/>
       <c r="I498" s="1"/>
@@ -16090,7 +16090,7 @@
       <c r="E499" s="2"/>
       <c r="F499" s="2"/>
       <c r="G499" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H499" s="1"/>
       <c r="I499" s="1"/>
@@ -16118,7 +16118,7 @@
       <c r="E500" s="2"/>
       <c r="F500" s="2"/>
       <c r="G500" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H500" s="1"/>
       <c r="I500" s="1"/>
@@ -16146,7 +16146,7 @@
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H501" s="1"/>
       <c r="I501" s="1"/>
@@ -16174,7 +16174,7 @@
       <c r="E502" s="2"/>
       <c r="F502" s="2"/>
       <c r="G502" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H502" s="1"/>
       <c r="I502" s="1"/>
@@ -16202,7 +16202,7 @@
       <c r="E503" s="2"/>
       <c r="F503" s="2"/>
       <c r="G503" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H503" s="1"/>
       <c r="I503" s="1"/>
@@ -16230,7 +16230,7 @@
       <c r="E504" s="2"/>
       <c r="F504" s="2"/>
       <c r="G504" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H504" s="1"/>
       <c r="I504" s="1"/>
@@ -16258,7 +16258,7 @@
       <c r="E505" s="2"/>
       <c r="F505" s="2"/>
       <c r="G505" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H505" s="1"/>
       <c r="I505" s="1"/>
@@ -16286,10 +16286,10 @@
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
       <c r="G506" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H506" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I506" s="1"/>
       <c r="J506" s="1"/>
@@ -16316,10 +16316,10 @@
       <c r="E507" s="2"/>
       <c r="F507" s="2"/>
       <c r="G507" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H507" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I507" s="1"/>
       <c r="J507" s="1"/>
@@ -16346,10 +16346,10 @@
       <c r="E508" s="2"/>
       <c r="F508" s="2"/>
       <c r="G508" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I508" s="1"/>
       <c r="J508" s="1"/>
@@ -16376,10 +16376,10 @@
       <c r="E509" s="2"/>
       <c r="F509" s="2"/>
       <c r="G509" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I509" s="1"/>
       <c r="J509" s="1"/>
@@ -16406,10 +16406,10 @@
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H510" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H510" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I510" s="1"/>
       <c r="J510" s="1"/>
@@ -16436,10 +16436,10 @@
       <c r="E511" s="2"/>
       <c r="F511" s="2"/>
       <c r="G511" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I511" s="1"/>
       <c r="J511" s="1"/>
@@ -16466,10 +16466,10 @@
       <c r="E512" s="1"/>
       <c r="F512" s="1"/>
       <c r="G512" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I512" s="1"/>
       <c r="J512" s="1"/>
@@ -16496,10 +16496,10 @@
       <c r="E513" s="1"/>
       <c r="F513" s="1"/>
       <c r="G513" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I513" s="1"/>
       <c r="J513" s="1"/>
@@ -16526,10 +16526,10 @@
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I514" s="1"/>
       <c r="J514" s="1"/>
@@ -16556,10 +16556,10 @@
       <c r="E515" s="2"/>
       <c r="F515" s="2"/>
       <c r="G515" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I515" s="1"/>
       <c r="J515" s="1"/>
@@ -16586,10 +16586,10 @@
       <c r="E516" s="2"/>
       <c r="F516" s="2"/>
       <c r="G516" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I516" s="1"/>
       <c r="J516" s="1"/>
@@ -16616,10 +16616,10 @@
       <c r="E517" s="1"/>
       <c r="F517" s="1"/>
       <c r="G517" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I517" s="1"/>
       <c r="J517" s="1"/>
@@ -16646,10 +16646,10 @@
       <c r="E518" s="1"/>
       <c r="F518" s="1"/>
       <c r="G518" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I518" s="1"/>
       <c r="J518" s="1"/>
@@ -16676,10 +16676,10 @@
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I519" s="1"/>
       <c r="J519" s="1"/>
@@ -16706,10 +16706,10 @@
       <c r="E520" s="2"/>
       <c r="F520" s="2"/>
       <c r="G520" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I520" s="1"/>
       <c r="J520" s="1"/>
@@ -16736,10 +16736,10 @@
       <c r="E521" s="2"/>
       <c r="F521" s="2"/>
       <c r="G521" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I521" s="1"/>
       <c r="J521" s="1"/>
@@ -16766,10 +16766,10 @@
       <c r="E522" s="1"/>
       <c r="F522" s="1"/>
       <c r="G522" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I522" s="1"/>
       <c r="J522" s="1"/>
@@ -16796,10 +16796,10 @@
       <c r="E523" s="1"/>
       <c r="F523" s="1"/>
       <c r="G523" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I523" s="1"/>
       <c r="J523" s="1"/>
@@ -16826,7 +16826,7 @@
       <c r="E524" s="2"/>
       <c r="F524" s="2"/>
       <c r="G524" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H524" s="1"/>
       <c r="I524" s="1"/>
@@ -16854,7 +16854,7 @@
       <c r="E525" s="2"/>
       <c r="F525" s="2"/>
       <c r="G525" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H525" s="1"/>
       <c r="I525" s="1"/>
@@ -16882,7 +16882,7 @@
       <c r="E526" s="2"/>
       <c r="F526" s="2"/>
       <c r="G526" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H526" s="1"/>
       <c r="I526" s="1"/>
@@ -16910,7 +16910,7 @@
       <c r="E527" s="2"/>
       <c r="F527" s="2"/>
       <c r="G527" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H527" s="1"/>
       <c r="I527" s="1"/>
@@ -16938,7 +16938,7 @@
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H528" s="1"/>
       <c r="I528" s="1"/>
@@ -16966,7 +16966,7 @@
       <c r="E529" s="2"/>
       <c r="F529" s="2"/>
       <c r="G529" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H529" s="1"/>
       <c r="I529" s="1"/>
@@ -16994,7 +16994,7 @@
       <c r="E530" s="2"/>
       <c r="F530" s="2"/>
       <c r="G530" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H530" s="1"/>
       <c r="I530" s="1"/>
@@ -17022,7 +17022,7 @@
       <c r="E531" s="2"/>
       <c r="F531" s="2"/>
       <c r="G531" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H531" s="1"/>
       <c r="I531" s="1"/>
@@ -17050,7 +17050,7 @@
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H532" s="1"/>
       <c r="I532" s="1"/>
@@ -17078,7 +17078,7 @@
       <c r="E533" s="2"/>
       <c r="F533" s="2"/>
       <c r="G533" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H533" s="1"/>
       <c r="I533" s="1"/>
@@ -17106,7 +17106,7 @@
       <c r="E534" s="2"/>
       <c r="F534" s="2"/>
       <c r="G534" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H534" s="1"/>
       <c r="I534" s="1"/>
@@ -17134,10 +17134,10 @@
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
       <c r="G535" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H535" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I535" s="1"/>
       <c r="J535" s="1"/>
@@ -17164,10 +17164,10 @@
       <c r="E536" s="2"/>
       <c r="F536" s="2"/>
       <c r="G536" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H536" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I536" s="1"/>
       <c r="J536" s="1"/>
@@ -17194,10 +17194,10 @@
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I537" s="1"/>
       <c r="J537" s="1"/>
@@ -17224,10 +17224,10 @@
       <c r="E538" s="2"/>
       <c r="F538" s="2"/>
       <c r="G538" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I538" s="1"/>
       <c r="J538" s="1"/>
@@ -17254,10 +17254,10 @@
       <c r="E539" s="2"/>
       <c r="F539" s="2"/>
       <c r="G539" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H539" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H539" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I539" s="1"/>
       <c r="J539" s="1"/>
@@ -17284,10 +17284,10 @@
       <c r="E540" s="2"/>
       <c r="F540" s="2"/>
       <c r="G540" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H540" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I540" s="1"/>
       <c r="J540" s="1"/>
@@ -17314,10 +17314,10 @@
       <c r="E541" s="1"/>
       <c r="F541" s="1"/>
       <c r="G541" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H541" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I541" s="1"/>
       <c r="J541" s="1"/>
@@ -17344,10 +17344,10 @@
       <c r="E542" s="1"/>
       <c r="F542" s="1"/>
       <c r="G542" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H542" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I542" s="1"/>
       <c r="J542" s="1"/>
@@ -17374,10 +17374,10 @@
       <c r="E543" s="2"/>
       <c r="F543" s="2"/>
       <c r="G543" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H543" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I543" s="1"/>
       <c r="J543" s="1"/>
@@ -17404,10 +17404,10 @@
       <c r="E544" s="2"/>
       <c r="F544" s="2"/>
       <c r="G544" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H544" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I544" s="1"/>
       <c r="J544" s="1"/>
@@ -17434,10 +17434,10 @@
       <c r="E545" s="2"/>
       <c r="F545" s="2"/>
       <c r="G545" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H545" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I545" s="1"/>
       <c r="J545" s="1"/>
@@ -17464,10 +17464,10 @@
       <c r="E546" s="1"/>
       <c r="F546" s="1"/>
       <c r="G546" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H546" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I546" s="1"/>
       <c r="J546" s="1"/>
@@ -17494,10 +17494,10 @@
       <c r="E547" s="1"/>
       <c r="F547" s="1"/>
       <c r="G547" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H547" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I547" s="1"/>
       <c r="J547" s="1"/>
@@ -17524,10 +17524,10 @@
       <c r="E548" s="2"/>
       <c r="F548" s="2"/>
       <c r="G548" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I548" s="1"/>
       <c r="J548" s="1"/>
@@ -17554,10 +17554,10 @@
       <c r="E549" s="2"/>
       <c r="F549" s="2"/>
       <c r="G549" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I549" s="1"/>
       <c r="J549" s="1"/>
@@ -17584,10 +17584,10 @@
       <c r="E550" s="2"/>
       <c r="F550" s="2"/>
       <c r="G550" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I550" s="1"/>
       <c r="J550" s="1"/>
@@ -17614,10 +17614,10 @@
       <c r="E551" s="1"/>
       <c r="F551" s="1"/>
       <c r="G551" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I551" s="1"/>
       <c r="J551" s="1"/>
@@ -17644,10 +17644,10 @@
       <c r="E552" s="1"/>
       <c r="F552" s="1"/>
       <c r="G552" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H552" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I552" s="1"/>
       <c r="J552" s="1"/>
@@ -17674,7 +17674,7 @@
       <c r="E553" s="2"/>
       <c r="F553" s="2"/>
       <c r="G553" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H553" s="1"/>
       <c r="I553" s="1"/>
@@ -17702,7 +17702,7 @@
       <c r="E554" s="2"/>
       <c r="F554" s="2"/>
       <c r="G554" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H554" s="1"/>
       <c r="I554" s="1"/>
@@ -17730,7 +17730,7 @@
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H555" s="1"/>
       <c r="I555" s="1"/>
@@ -17758,7 +17758,7 @@
       <c r="E556" s="2"/>
       <c r="F556" s="2"/>
       <c r="G556" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H556" s="1"/>
       <c r="I556" s="1"/>
@@ -17786,7 +17786,7 @@
       <c r="E557" s="2"/>
       <c r="F557" s="2"/>
       <c r="G557" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H557" s="1"/>
       <c r="I557" s="1"/>
@@ -17814,7 +17814,7 @@
       <c r="E558" s="2"/>
       <c r="F558" s="2"/>
       <c r="G558" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H558" s="1"/>
       <c r="I558" s="1"/>
@@ -17842,7 +17842,7 @@
       <c r="E559" s="2"/>
       <c r="F559" s="2"/>
       <c r="G559" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H559" s="1"/>
       <c r="I559" s="1"/>
@@ -17870,7 +17870,7 @@
       <c r="E560" s="2"/>
       <c r="F560" s="2"/>
       <c r="G560" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H560" s="1"/>
       <c r="I560" s="1"/>
@@ -17898,7 +17898,7 @@
       <c r="E561" s="2"/>
       <c r="F561" s="2"/>
       <c r="G561" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H561" s="1"/>
       <c r="I561" s="1"/>
@@ -17926,7 +17926,7 @@
       <c r="E562" s="2"/>
       <c r="F562" s="2"/>
       <c r="G562" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H562" s="1"/>
       <c r="I562" s="1"/>
@@ -17954,7 +17954,7 @@
       <c r="E563" s="2"/>
       <c r="F563" s="2"/>
       <c r="G563" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H563" s="1"/>
       <c r="I563" s="1"/>
@@ -17982,10 +17982,10 @@
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
       <c r="G564" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H564" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I564" s="1"/>
       <c r="J564" s="1"/>
@@ -18012,10 +18012,10 @@
       <c r="E565" s="2"/>
       <c r="F565" s="2"/>
       <c r="G565" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H565" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I565" s="1"/>
       <c r="J565" s="1"/>
@@ -18042,10 +18042,10 @@
       <c r="E566" s="2"/>
       <c r="F566" s="2"/>
       <c r="G566" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I566" s="1"/>
       <c r="J566" s="1"/>
@@ -18072,10 +18072,10 @@
       <c r="E567" s="2"/>
       <c r="F567" s="2"/>
       <c r="G567" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I567" s="1"/>
       <c r="J567" s="1"/>
@@ -18102,10 +18102,10 @@
       <c r="E568" s="2"/>
       <c r="F568" s="2"/>
       <c r="G568" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H568" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H568" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="I568" s="1"/>
       <c r="J568" s="1"/>
@@ -18132,10 +18132,10 @@
       <c r="E569" s="2"/>
       <c r="F569" s="2"/>
       <c r="G569" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H569" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I569" s="1"/>
       <c r="J569" s="1"/>
@@ -18162,10 +18162,10 @@
       <c r="E570" s="1"/>
       <c r="F570" s="1"/>
       <c r="G570" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H570" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="I570" s="1"/>
       <c r="J570" s="1"/>
@@ -18192,10 +18192,10 @@
       <c r="E571" s="1"/>
       <c r="F571" s="1"/>
       <c r="G571" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H571" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I571" s="1"/>
       <c r="J571" s="1"/>
@@ -18222,10 +18222,10 @@
       <c r="E572" s="2"/>
       <c r="F572" s="2"/>
       <c r="G572" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H572" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I572" s="1"/>
       <c r="J572" s="1"/>
@@ -18252,10 +18252,10 @@
       <c r="E573" s="2"/>
       <c r="F573" s="2"/>
       <c r="G573" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H573" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I573" s="1"/>
       <c r="J573" s="1"/>
@@ -18282,10 +18282,10 @@
       <c r="E574" s="2"/>
       <c r="F574" s="2"/>
       <c r="G574" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I574" s="1"/>
       <c r="J574" s="1"/>
@@ -18312,10 +18312,10 @@
       <c r="E575" s="1"/>
       <c r="F575" s="1"/>
       <c r="G575" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H575" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I575" s="1"/>
       <c r="J575" s="1"/>
@@ -18342,10 +18342,10 @@
       <c r="E576" s="1"/>
       <c r="F576" s="1"/>
       <c r="G576" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H576" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I576" s="1"/>
       <c r="J576" s="1"/>
@@ -18372,10 +18372,10 @@
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H577" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I577" s="1"/>
       <c r="J577" s="1"/>
@@ -18402,10 +18402,10 @@
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H578" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I578" s="1"/>
       <c r="J578" s="1"/>
@@ -18432,10 +18432,10 @@
       <c r="E579" s="2"/>
       <c r="F579" s="2"/>
       <c r="G579" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H579" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I579" s="1"/>
       <c r="J579" s="1"/>
@@ -18462,10 +18462,10 @@
       <c r="E580" s="1"/>
       <c r="F580" s="1"/>
       <c r="G580" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H580" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I580" s="1"/>
       <c r="J580" s="1"/>
@@ -18492,10 +18492,10 @@
       <c r="E581" s="1"/>
       <c r="F581" s="1"/>
       <c r="G581" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H581" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I581" s="1"/>
       <c r="J581" s="1"/>
@@ -18522,7 +18522,7 @@
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H582" s="1"/>
       <c r="I582" s="1"/>
@@ -18550,7 +18550,7 @@
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H583" s="1"/>
       <c r="I583" s="1"/>
@@ -18578,7 +18578,7 @@
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H584" s="1"/>
       <c r="I584" s="1"/>
@@ -18606,7 +18606,7 @@
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
       <c r="G585" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H585" s="1"/>
       <c r="I585" s="1"/>
@@ -18634,7 +18634,7 @@
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
       <c r="G586" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H586" s="1"/>
       <c r="I586" s="1"/>
@@ -18662,7 +18662,7 @@
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
       <c r="G587" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H587" s="1"/>
       <c r="I587" s="1"/>
@@ -18690,7 +18690,7 @@
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
       <c r="G588" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H588" s="1"/>
       <c r="I588" s="1"/>
@@ -18718,7 +18718,7 @@
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
       <c r="G589" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H589" s="1"/>
       <c r="I589" s="1"/>
@@ -18746,7 +18746,7 @@
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
       <c r="G590" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H590" s="1"/>
       <c r="I590" s="1"/>
@@ -18774,7 +18774,7 @@
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
       <c r="G591" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H591" s="1"/>
       <c r="I591" s="1"/>
@@ -18802,7 +18802,7 @@
       <c r="E592" s="2"/>
       <c r="F592" s="2"/>
       <c r="G592" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H592" s="1"/>
       <c r="I592" s="1"/>
